--- a/Source/BCIO-source-hierarchy.xlsx
+++ b/Source/BCIO-source-hierarchy.xlsx
@@ -445,32 +445,32 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
+          <t>subontology</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>informaldefinition</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>examples</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>informaldefinition</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>synonyms</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>subontology</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>crossreference</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>examples</t>
         </is>
       </c>
     </row>
@@ -533,13 +533,13 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BFO:0000002</t>
+          <t>BFO:0000003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>continuant</t>
+          <t>occurrent</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -554,21 +554,21 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>An entity that exists in full at any time in which it exists at all, persists through time while maintaining its identity and has no temporal parts.</t>
+          <t>An entity that has temporal parts and that happens, unfolds or develops through time.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BFO:0000031</t>
+          <t>BFO:0000015</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>generically dependent continuant</t>
+          <t>process</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -582,14 +582,14 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>b is a generically dependent continuant = Def. b is a continuant that g-depends_on one or more other entities. (axiom label in BFO2 Reference: [074-001])</t>
+          <t>p is a process = Def. p is an occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t. (axiom label in BFO2 Reference: [083-003])</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IAO:0000030</t>
+          <t>BCIO:010130</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -597,7 +597,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>information content entity</t>
+          <t>payment of person source</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -610,14 +610,22 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>A generically dependent continuant that is about some thing.</t>
-        </is>
-      </c>
+          <t>A process in which a person source is paid or compensated for delivering the intervention.</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IAO:0000027</t>
+          <t>BCIO:010131</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -626,7 +634,7 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>data item</t>
+          <t>monetary payment</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -638,26 +646,38 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>An information content entity that is intended to be a truthful statement about something (modulo, e.g., measurement precision or other systematic errors) and is constructed/acquired by a method which reliably tends to produce (approximately) truthful statements.</t>
-        </is>
-      </c>
+          <t>A payment of person source that is money, vouchers or valued objects given to the source for delivering the intervention.</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>paid in cash, vouchers</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BCIO:010126</t>
+          <t>BCIO:010132</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>amount of experience</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>non-monetary payment</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
@@ -666,38 +686,38 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>A knowledge or skill that is the duration of experience in related domain held by person source.</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A payment of person source that is non-monetary compensation given to the source for delivering the intervention.</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>course credit</t>
         </is>
       </c>
       <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>full-day, 6 years</t>
-        </is>
-      </c>
+      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BCIO:010106</t>
+          <t>BCIO:010129</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>volunteering of person source</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>number of people delivering intervention to each participant</t>
-        </is>
-      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
@@ -706,13 +726,17 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>A count data item that is the number of providers that an individual participant in the intervention encounters.</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A process in which a person source delivers the intervention on a voluntary basis without formal compensation.</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>voluntary basis, volunteering</t>
         </is>
       </c>
       <c r="S9" t="inlineStr"/>
@@ -721,19 +745,19 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BCIO:010107</t>
+          <t>BCIO:010128</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>supervision of person source</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>total number of people able to deliver intervention</t>
-        </is>
-      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
@@ -742,13 +766,17 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>A count data item that is the total number of providers that are available and able to deliver the intervention.</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A process in which a person source is formally provided, by an individual with appropriate expertise, with corrective and skill-enhancing feedback, regarding the person source’s performance in delivering the intervention.</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>supervised</t>
         </is>
       </c>
       <c r="S10" t="inlineStr"/>
@@ -757,16 +785,16 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BFO:0000004</t>
+          <t>BFO:0000002</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>independent continuant</t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>continuant</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
@@ -778,24 +806,24 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>A continuant that is a bearer of quality and realizable entity entities, in which other entities inhere and which itself cannot inhere in anything.</t>
+          <t>An entity that exists in full at any time in which it exists at all, persists through time while maintaining its identity and has no temporal parts.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BFO:0000040</t>
+          <t>BFO:0000020</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>material entity</t>
-        </is>
-      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>characteristic</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
@@ -806,25 +834,25 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>An &lt;independent continuant&gt; that is spatially extended whose identity is independent of that of other entities and can be maintained through time.</t>
+          <t>b is a specifically dependent continuant = Def. b is a continuant and there is some independent continuant c which is not a spatial region and which is such that b s-depends_on c at every time t during the course of b’s existence. (axiom label in BFO2 Reference: [050-003])</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>OGMS:0000087</t>
+          <t>BCIO:010123</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>extended organism</t>
-        </is>
-      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>expertise discipline</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
@@ -834,26 +862,43 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>An object aggregate consisting of an organism and all material entities located within the organism, overlapping the organism, or occupying sites formed in part by the organism.</t>
-        </is>
-      </c>
+          <t>An attribute that is a field of knowledge or practice.</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>psychology, yoga, cognitive behavioural therapy, hypnotism</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>The division of expertise into different disciplines or fields is complex and depends on historical, social and structural factors.</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MF:0000016</t>
+          <t>BCIO:010093</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>human being</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>discipline of current programme of study or training</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
@@ -862,13 +907,17 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>An extended organism that is a member of the species Homo sapiens.</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>An expertise discipline of the programme of study currently undertaken by the bearer of a student or trainee role.</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>psychology, medicine, hairdressing</t>
         </is>
       </c>
       <c r="S14" t="inlineStr"/>
@@ -877,20 +926,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BCIO:010002</t>
+          <t>BCIO:010124</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>discipline of pre-existing expertise</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>person source</t>
-        </is>
-      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
@@ -898,13 +947,17 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>A person who is the bearer of a behaviour change intervention source role.</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>The expertise discipline in which the person source has acquired their pre-existing knowledge and skills.</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>psychology, yoga, cognitive behavioural therapy, hypnotism</t>
         </is>
       </c>
       <c r="S15" t="inlineStr"/>
@@ -913,20 +966,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BCIO:010095</t>
+          <t>BFO:0000017</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>realizable entity</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>family member</t>
-        </is>
-      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
@@ -934,62 +987,42 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>A person who is a member of a group of persons united by blood, or by marriage or other legal arrangement, or by self-identity as belonging to the same family.</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
+          <t>A specifically dependent continuant  that inheres in continuant  entities and are not exhibited in full at every time in which it inheres in an entity or group of entities. The exhibition or actualization of a realizable entity is a particular manifestation, functioning or process that occurs under certain circumstances.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BCIO:010099</t>
+          <t>BFO:0000023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>child relationship</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>A family member that is an offspring relationship from a person to their parent.</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>daughter, son, step-daughter, step-son</t>
+          <t>A realizable entity  the manifestation of which brings about some result or end that is not essential to a continuant  in virtue of the kind of thing that it is but that can be served or participated in by that kind of continuant  in some kinds of natural, social or institutional contexts.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BCIO:010098</t>
+          <t>BCIO:010003</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -997,39 +1030,35 @@
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>personal role of source</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>sibling relationship</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>A family member that is a family relationship between two persons with at least one shared parent.</t>
+          <t>A role that inheres in a person source.</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
       <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>brother, sister, step-brother, step-sister</t>
-        </is>
-      </c>
+      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BCIO:010096</t>
+          <t>BCIO:010094</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -1038,38 +1067,34 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>parent or guardian</t>
-        </is>
-      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>relatedness between person source and the target population</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>A family member that is a mother, father or legal carer of a child.</t>
+          <t>A personal role of source that is realised in some relationship to the characteristics of the intervention participants.</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
       <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>mother, father, step-mother, step-father, guardian</t>
-        </is>
-      </c>
+      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BCIO:010097</t>
+          <t>BCIO:010102</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -1081,7 +1106,7 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>spouse or partner</t>
+          <t>colleague</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -1090,26 +1115,22 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>A family member that is an individual who is married or in a committed relationship with another individual.</t>
+          <t>A relatedness between person source and the target population that is a person with whom the participant works in a profession or business.</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
       <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>boyfriend, girlfriend, partner, fiance, wife, husband</t>
-        </is>
-      </c>
+      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BCIO:050842</t>
+          <t>BCIO:010101</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1118,102 +1139,101 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>role model for a person</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>A &lt;person&gt; that influences a recipient by being perceived to be similar or admired.</t>
+          <t>A relatedness between person source and the target population that is a person whom the participant knows, likes and trusts, typically exclusive of sexual or family relations.</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>This class lies at the intersection between a person and their environment and is defined from the perspective of the person.</t>
+          <t>Source</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BCIO:010139</t>
+          <t>BCIO:010104</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>organisation source</t>
-        </is>
-      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>peer</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>An organisation that is the bearer of a behaviour change intervention source role, such as voluntary, public or commercial organisations delivering a behaviour change intervention.</t>
+          <t>A relatedness between person source and the target population that is descried as matched to intervention recipients on the basis of ‘peerness’ – age, social status, gender, shared experience, shared health status etc.</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>OBI:0000245</t>
+          <t>BCIO:010100</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>organisation</t>
-        </is>
-      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>carer</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>An entity that can bear roles, has members, and has a set of organization rules. Members of organizations are either organizations themselves or individual people. Members can bear specific organization member roles that are determined in the organization rules. The organization rules also determine how decisions are made on behalf of the organization by the organization members.</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A relatedness between person source and the target population that is an individual who cares, unpaid, for a friend or family member who, due to illness or disability, requires support in their daily life activities.</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>carer</t>
         </is>
       </c>
       <c r="S23" t="inlineStr"/>
@@ -1222,76 +1242,92 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BFO:0000020</t>
+          <t>BCIO:010105</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>specifically dependent continuant</t>
-        </is>
-      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>embedded in participants’ community</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>b is a relational specifically dependent continuant = Def. b is a specifically dependent continuant and there are n &amp;gt; 1 independent continuants c1, … cn which are not spatial regions are such that for all 1  i &amp;lt; j  n, ci  and cj share no common parts, are such that for each 1  i  n, b s-depends_on ci at every time t during the course of b’s existence (axiom label in BFO2 Reference: [131-004])</t>
-        </is>
-      </c>
+          <t>A relatedness between person source and the target population that is a source who is known and working to deliver intervention in own community.</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BFO:0000017</t>
+          <t>BCIO:010103</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>realizable entity</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>employer</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>A specifically dependent continuant  that inheres in continuant  entities and are not exhibited in full at every time in which it inheres in an entity or group of entities. The exhibition or actualization of a realizable entity is a particular manifestation, functioning or process that occurs under certain circumstances.</t>
-        </is>
-      </c>
+          <t>A relatedness between person source and the target population that is a person which hires the services of the participant.</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BFO:0000023</t>
+          <t>BCIO:010004</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>role</t>
-        </is>
-      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>occupational role of source</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
@@ -1299,14 +1335,26 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>A realizable entity  the manifestation of which brings about some result or end that is not essential to a continuant  in virtue of the kind of thing that it is but that can be served or participated in by that kind of continuant  in some kinds of natural, social or institutional contexts.</t>
-        </is>
-      </c>
+          <t>A personal role of source that is realised by doing a specified type of work or working in a specified way.</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Interventionist, facilitator, study staff</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BCIO:006081</t>
+          <t>BCIO:010082</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1314,35 +1362,39 @@
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>personal role</t>
-        </is>
-      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>armed forces occupation</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>A role that inheres in a human being by virtue of their social and institutional circumstances.</t>
+          <t>An occupational role that includes all jobs held by members of the armed forces.</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>A role can be assigned without being realised. A person realises a role by doing something.</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr"/>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Admiral, Air commodore, Air marshal, Airman, Brigadier (army), Bombardier, Captain (air force), Captain (army), Captain (navy), Colonel (army), Corporal,  Field marshal, Flight lieutenant (air force), Flying officer (military), General (army), Gunner, Group captain, (air force), Lieutenant (army), Major (army), Midshipman, Naval officer (military) , Navy commander, Officer cadet (armed forces), Paratrooper, Rifleman, Sergeant (army), Second lieutenant (army), Seaman, Squadron leader, Sublieutenant (navy), Wing commander</t>
+        </is>
+      </c>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BCIO:010084</t>
+          <t>BCIO:010067</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1351,25 +1403,29 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>student or trainee role</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>clerical support worker</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>A personal role which inheres in a person and is realised by being enrolled in an educational institution or a formal programme of professional training.</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>An occupational role that records, organizes, stores, computes and retrieves information, and performs a number of clerical duties in connection with money-handling operations, travel arrangements, requests for information, and appointments.</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>General and Keyboard Clerk, customers Services Clerk, Numerical and Material Recording Clerk</t>
         </is>
       </c>
       <c r="S28" t="inlineStr"/>
@@ -1378,7 +1434,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BCIO:010086</t>
+          <t>BCIO:010068</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1390,7 +1446,7 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>school student role</t>
+          <t>services and sales worker</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
@@ -1399,22 +1455,22 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>A student or trainee role realised by currently learning at a primary or secondary education level in an institutional, organised setting.</t>
+          <t>An occupational role that provides personal or protective services related to travel, house-keeping, catering, personal care, protection against fire and unlawful acts, or sells goods in retail or markets.</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BCIO:010087</t>
+          <t>BCIO:010076</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1424,24 +1480,28 @@
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>trainee role</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>protective services worker</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>A student or trainee role that is currently learning the curriculum material of vocational programme, normally in preparation for employment in a trade, job or profession.</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A services and sales worker that protects individuals and property against fire and other hazards, maintain law and order and enforce laws and regulations.</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Firefighter, Police officer, Prison guard, Security guard, Offender manager</t>
         </is>
       </c>
       <c r="S30" t="inlineStr"/>
@@ -1450,7 +1510,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BCIO:010085</t>
+          <t>BCIO:010070</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1460,24 +1520,28 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>informal education student role</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>sales worker</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>A student or trainee role that is currently learning in a non-institutional setting.</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A services and sales worker that demonstrates goods in wholesale or retail shops, at stalls and markets, door to door, via telephone or customer contact centres. They may record and accept payment for goods and services purchased, and may operate small retail outlets.</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Street Salesperson, Market Salesperson, Shop Salesperson, Cashier, Ticket Clerk, Model, Sales Demonstrator, Door-to-door Salesperson, Contact Centre Salesperson, Service Station Attendant, Food Service Counter Attendant</t>
         </is>
       </c>
       <c r="S31" t="inlineStr"/>
@@ -1486,7 +1550,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BCIO:010088</t>
+          <t>BCIO:010069</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1496,37 +1560,37 @@
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>higher education student role</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>personal services worker</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>A student or trainee role realised by currently learning on an advanced educational programme in a university, college or professional school.</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A services and sales worker that provides personal services related to travel, housekeeping, catering and hospitality, hairdressing and beauty treatment, animal care grooming and training, companionship and other services of a personal nature.</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Travel Attendant, Conductor, Guide, Cook, Waiter, Bartender, Hairdresser, Beautician, Housekeeping Supervisor, Astrologer, Fortune-teller, Valet, Undertaker, Embalmer, Pet Groomer, Animal Care Worker</t>
         </is>
       </c>
       <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>completing a university bachelor's or master's course of study, medical school or other professional school.</t>
-        </is>
-      </c>
+      <c r="T32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BCIO:010092</t>
+          <t>BCIO:010071</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1539,7 +1603,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>doctoral student role</t>
+          <t>personal care worker</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -1547,26 +1611,26 @@
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>A higher education student  role realised by currently studying for a doctoral degree.</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A services and sales worker that provides care, supervision and assistance for children, patients and elderly, convalescent or disabled persons in institutional and residential settings.</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Personal carer</t>
         </is>
       </c>
       <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>PhD student</t>
-        </is>
-      </c>
+      <c r="T33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BCIO:010090</t>
+          <t>BCIO:010074</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1577,36 +1641,36 @@
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>graduate student role</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>health care assistant</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>A higher education student role realised by currently studying for a more advanced degree after completing an undergraduate degree.</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A personal care worker that provides direct personal care and assistance with activities of daily living to patients and residents in a variety of health care settings, working  in implementation of established care plans and practices, and under the direct supervision of medical, nursing or other health professionals or associate professionals.</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Nursing aide (clinic or hospital), Patient care assistant, Psychiatric aid</t>
         </is>
       </c>
       <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>graduate student</t>
-        </is>
-      </c>
+      <c r="T34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BCIO:010089</t>
+          <t>BCIO:010073</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1617,36 +1681,36 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>undergraduate student role</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>teachers’ aide</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>A higher education student role realised by currently studying for an undergraduate degree.</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A personal care worker that performs non-teaching duties to assist teaching staff, and provides care and supervision for children in schools and pre-schools.</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Pre-school assistant, Teacher’s assistant</t>
         </is>
       </c>
       <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>undergraduate student</t>
-        </is>
-      </c>
+      <c r="T35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BCIO:010091</t>
+          <t>BCIO:010075</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1657,36 +1721,36 @@
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>masters student role</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>home-based personal care worker</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>A higher education student  role realised by currently studying for a masters degree.</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A personal care worker that provide routine personal care and assistance with activities of daily living to persons who are in need of such care due to effects of ageing, illness, injury, or other physical or mental conditions, in private homes and other independent residential settings.</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Home birth assistant, Home care aide, Nursing aide (home), Personal care provider</t>
         </is>
       </c>
       <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>MSc student, Masters student</t>
-        </is>
-      </c>
+      <c r="T36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BCIO:051024</t>
+          <t>BCIO:010072</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1695,29 +1759,38 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>certified professional role</t>
-        </is>
-      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>child care worker</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>A personal role that inheres in a human being by virtue of formal recognition of their competence by a professional or regulatory body.</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr"/>
+          <t>A personal care worker that provides care and supervision for children in non-domestic settings.</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Babysitter, Child care worker, Creche ayah, Family day care worker, Nanny, Out of school hours care worker</t>
+        </is>
+      </c>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BCIO:010000</t>
+          <t>BCIO:010079</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1725,26 +1798,30 @@
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>behaviour change intervention source</t>
-        </is>
-      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>plant and machine operator</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>A role played by a person, population or organisation that provides a BCI.</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>An occupational role that operates and monitors industrial and agricultural machinery and equipment on the spot or by remote control, or drives and operates trains, motor vehicles and mobile machinery and equipment.</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Stationary Plant and Machine Operator, Driver, Mobile Plant Operator</t>
         </is>
       </c>
       <c r="S38" t="inlineStr"/>
@@ -1753,7 +1830,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BCIO:010133</t>
+          <t>BCIO:010081</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1762,25 +1839,29 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>source role related to intervention</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>elementary occupation</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>A BCI source whose occupational or voluntary role is focused on delivery of the behaviour change intervention.</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>An occupational role that involves the performance of simple and routine tasks which may require the use of hand-held tools and considerable physical effort.</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Cleaner, Labourer, Food Preparation Assistant, Street and Related Services Worker, Street Vendor (excluding Food), Refuse Worker</t>
         </is>
       </c>
       <c r="S39" t="inlineStr"/>
@@ -1789,7 +1870,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BCIO:010134</t>
+          <t>BCIO:010005</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1798,25 +1879,29 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>source involved in development of intervention</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>manager</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>A BCI source that is involved in the development of intervention content.</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>An occupational role of source that manages, plans and coordinates the overall activities of enterprises, governments and other organisations.</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Chief Executive Officers; Administrative Managers;  Commercial Managers</t>
         </is>
       </c>
       <c r="S40" t="inlineStr"/>
@@ -1825,7 +1910,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BCIO:010135</t>
+          <t>BCIO:010006</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1837,7 +1922,7 @@
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>source involved in co-production of intervention</t>
+          <t>professional</t>
         </is>
       </c>
       <c r="J41" t="inlineStr"/>
@@ -1846,22 +1931,22 @@
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>A source involved in development of intervention that has developed the intervention content in collaboration with key stakeholders such as patients or community members.</t>
+          <t>An occupational role that works in knowledge building activities, applies scientific or artistic concepts and theories or teaches about the foregoing in a systematic manner.</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BCIO:010138</t>
+          <t>BCIO:010044</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1870,34 +1955,34 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>organisational source role</t>
-        </is>
-      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>technician and associate professional</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>A BCI source role that is borne by an organisation.</t>
+          <t>A professional that performs technical and related tasks connected with research and the application of scientific or artistic concepts and operational methods, and government or business regulations.</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BCIO:010001</t>
+          <t>BCIO:010058</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -1906,25 +1991,29 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>person source role</t>
-        </is>
-      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>legal and related associate professional</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>A behaviour change intervention source role that inheres in a person.</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A technician and associate professional that performs support functions in courts of law or in law offices, provide services related to such legal matters as insurance contracts, the transferring of property and the granting of loans and other financial transactions, or conduct investigations for clients.</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>Bailiff, Judge’s clerk, Conveyancing clerk, Court clerk, Justice of the peace, Law clerk, Legal assistant, Paralegal, Private detective, Title searcher</t>
         </is>
       </c>
       <c r="S43" t="inlineStr"/>
@@ -1933,7 +2022,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BCIO:010003</t>
+          <t>BCIO:010066</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1941,26 +2030,30 @@
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>personal role of source</t>
-        </is>
-      </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>information and communications technician</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>A role that inheres in a person source.</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A technician and associate professional that provides support for the day to day running of computer systems, communication systems and networks, broadcast images and sound, telecommunication signals on land, sea or in aircraft.</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>Information and Communications Technology Operations and User Support Technician, Telecommunications and Broadcasting Technician</t>
         </is>
       </c>
       <c r="S44" t="inlineStr"/>
@@ -1969,7 +2062,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BCIO:010004</t>
+          <t>BCIO:010065</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -1978,38 +2071,38 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>occupational role of source</t>
-        </is>
-      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>artistic, cultural and culinary associate professional</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>A personal role of source that is realised by doing a specified type of work or working in a specified way.</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A technician and associate professional that combines creative skills and technical and cultural knowledge in creative media or food.</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>Photographer, Interior designers and decorator, Gallery, museum and library technician, Chef</t>
         </is>
       </c>
       <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>Interventionist, facilitator, study staff</t>
-        </is>
-      </c>
+      <c r="T45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BCIO:010079</t>
+          <t>BCIO:010045</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -2019,37 +2112,37 @@
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>plant and machine operator</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>health associate professional</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t>An occupational role that operates and monitors industrial and agricultural machinery and equipment on the spot or by remote control, or drives and operates trains, motor vehicles and mobile machinery and equipment.</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A technician and associate professional that performs technical and practical tasks to support diagnosis and treatment of illness, disease, injuries and impairments in humans or animals, and supports the implementation of health care usually established by medical, veterinary, nursing and other health professionals.</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>Veterinary Technician</t>
         </is>
       </c>
       <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>Stationary Plant and Machine Operator, Driver, Mobile Plant Operator</t>
-        </is>
-      </c>
+      <c r="T46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BCIO:010083</t>
+          <t>BCIO:010056</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -2059,37 +2152,37 @@
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>researcher role</t>
-        </is>
-      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>ambulance worker</t>
+        </is>
+      </c>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>A occupational role played by a person that contributes substantively to production or reporting of a research study.</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A health associate professional that provides emergency health care to patients who are injured, sick, infirm or otherwise physically or mentally impaired prior to and during transport to medical facilities.</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Ambulance officer, Ambulance paramedic, Emergency medical technician, Emergency paramedic</t>
         </is>
       </c>
       <c r="S47" t="inlineStr"/>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>researcher, research assistant, investigator</t>
-        </is>
-      </c>
+      <c r="T47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BCIO:030000</t>
+          <t>BCIO:010046</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2100,27 +2193,36 @@
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>behaviour change intervention study investigator role</t>
-        </is>
-      </c>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>medical and pharmaceutical technician</t>
+        </is>
+      </c>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>A researcher role played by a person that contributes substantively to production or reporting of a BCI evaluation study.</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr"/>
+          <t>A health associate professional that performs technical tasks to assist in diagnosis and treatment of illness, disease, injuries and impairments.</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>Medical imaging and therapeutic equipment technician, Medical and Pathology laboratory technician, Pharmaceutical technician, Medical and dental prosthetic technician</t>
+        </is>
+      </c>
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BCIO:010006</t>
+          <t>BCIO:010052</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2130,24 +2232,28 @@
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>professional</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>community health worker</t>
+        </is>
+      </c>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>An occupational role that works in knowledge building activities, applies scientific or artistic concepts and theories or teaches about the foregoing in a systematic manner.</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A health associate professional that provides health education, referral and follow-up, case management, basic preventive health care and home visiting services to specific communities. They provide support and assistance to individuals and families in navigating the health and social services system.</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>Community health aide, Community health promoter, Community health worker, Village health worker, outreach worker, health worker</t>
         </is>
       </c>
       <c r="S49" t="inlineStr"/>
@@ -2156,7 +2262,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BCIO:010025</t>
+          <t>BCIO:010050</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2167,36 +2273,36 @@
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>teaching professional</t>
-        </is>
-      </c>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>traditional and complementary medicine associate professional</t>
+        </is>
+      </c>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t>A professional that teaches the theory and practice of one or more disciplines at different educational levels.</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A health associate professional that prevents and treats human physical and mental illnesses, disorders and injuries using herbal and other therapies based on theories, beliefs and experiences originating in specific cultures. They administer treatments using traditional techniques and medicaments, either acting independently or according to therapeutic care plans established by a traditional medicine or other health professional.</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>Acupuncture technician, Ayurvedic technician, Bonesetter, Herbalist , Homeopathy technician, Scraping and cupping therapist, Village healer, Witch doctor</t>
         </is>
       </c>
       <c r="S50" t="inlineStr"/>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>Education Methods Specialist, Other Language Teacher, Information Technology Teacher, Private Tutor, School Counsellor, Student Advisor</t>
-        </is>
-      </c>
+      <c r="T50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BCIO:010032</t>
+          <t>BCIO:010051</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2208,35 +2314,35 @@
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>music teacher</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>dental assistant and therapist</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>A teaching professional that teaches students in the practice, theory and performance of music in private or small group tuition or within mainstream educational institutions.</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A health associate professional that provides basic dental care services for the prevention and treatment of diseases and disorders of the teeth and mouth, according to care plans and procedures established by a dentist or other oral health professional.</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>Dental assistant, Dental hygienist , Dental therapist</t>
         </is>
       </c>
       <c r="S51" t="inlineStr"/>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>Guitar teacher (private tuition), Piano teacher (private tuition), Singing teacher (private tuition), Violin teacher (private tuition)</t>
-        </is>
-      </c>
+      <c r="T51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BCIO:010026</t>
+          <t>BCIO:010054</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2248,35 +2354,35 @@
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>university and higher education teacher</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>medical assistant</t>
+        </is>
+      </c>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>A teaching professional that prepares and delivers lectures and conduct tutorials in one or more subjects within a prescribed course of study at a university or other higher educational institution. They conduct research, and prepare scholarly papers and books.</t>
-        </is>
-      </c>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A health associate professional that performs basic clinical and administrative tasks to support patient care under the direct supervision of a medical practitioner or other health professional.</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>Clinical assistant, Medical assistant, Ophthalmic assistant</t>
         </is>
       </c>
       <c r="S52" t="inlineStr"/>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>Higher education lecturer, Professor, University lecturer, University tutor</t>
-        </is>
-      </c>
+      <c r="T52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BCIO:010027</t>
+          <t>BCIO:010053</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2288,35 +2394,35 @@
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>vocational education teacher</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>physiotherapy technician and assistant</t>
+        </is>
+      </c>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>A teaching professional that teaches or instructs vocational or occupational subjects in adult and further education institutions and to senior students in secondary schools and colleges.</t>
-        </is>
-      </c>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A health associate professional that provides physical therapeutic treatments to patients in circumstances where functional movement is threatened by injury, disease or impairment. Therapies are usually provided according to rehabilitative plans established by a physiotherapist or other health professional.</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>Acupressure therapist, Electrotherapist, Hydrotherapist, Massage therapist, Physical rehabilitation technician, Physiotherapy technician, Shiatsu therapist</t>
         </is>
       </c>
       <c r="S53" t="inlineStr"/>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>Automotive technology instructor, Cosmetology instructor, Vocational education teacher</t>
-        </is>
-      </c>
+      <c r="T53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BCIO:010031</t>
+          <t>BCIO:010055</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2328,35 +2434,36 @@
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>special needs teacher</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>environmental and occupational health inspector and associate</t>
+        </is>
+      </c>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>A teaching professional that teaches children, young persons or adults with physical or intellectual special needs.</t>
-        </is>
-      </c>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A health associate professional that investigates the implementation of rules and regulations relating to environmental factors that may affect human health, safety in the 
+workplace, and safety of processes for the production of goods and services. They may implement and evaluate programmes to restore or improve safety and sanitary conditions under the supervision of a health professional.</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>Food sanitation and safety inspector, Health inspector, Occupational health and safety inspector, Pollution inspector, Product safety inspector, Sanitarian, Sanitary inspector</t>
         </is>
       </c>
       <c r="S54" t="inlineStr"/>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>Learning disabilities special education teacher, Learning support teacher, Remedial teacher, Teacher of gifted children, Teacher of the hearing impaired, Teacher of the sight impaired</t>
-        </is>
-      </c>
+      <c r="T54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BCIO:010033</t>
+          <t>BCIO:010047</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2368,35 +2475,35 @@
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>arts teacher</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>nursing and midwifery associate professional</t>
+        </is>
+      </c>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t>A teaching professional  that teaches students in the practice, theory and performance of dance, drama, visual and other arts (excluding music) in private or small group tuition or within mainstream educational institutions.</t>
-        </is>
-      </c>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A health associate professional that provides basic nursing and personal care for people who are physically or mentally ill, disabled or infirm, and for others in need of care due to potential risks to health including before, during and after childbirth. They generally work under the supervision of, and in support of, implementation of health care, treatment and referrals plans established by medical, nursing, midwifery and other health professionals.</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>Practice assistant, Quit Smoking Counsellor, Health educator, Dispensing Optician, Information Technician</t>
         </is>
       </c>
       <c r="S55" t="inlineStr"/>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>Dance teacher (private tuition), Drama teacher (private tuition), Painting teacher (private tuition), Sculpture teacher (private tuition)</t>
-        </is>
-      </c>
+      <c r="T55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BCIO:010029</t>
+          <t>BCIO:010048</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2408,22 +2515,26 @@
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>primary school teacher</t>
-        </is>
-      </c>
+      <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>nursing associate professional</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>A teaching professional that teaches teach a range of subjects at the primary education level.</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A nursing and midwifery associate professional that provides basic nursing and personal care for people in need of such care due to effects of ageing, illness, injury, or other physical or mental impairment. They generally work under the supervision of, and in support of, implementation of health care, treatment and referrals plans established by medical, nursing and other health professionals.</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>Assistant nurse, Associate professional nurse, Enrolled nurse, Practical nurse</t>
         </is>
       </c>
       <c r="S56" t="inlineStr"/>
@@ -2432,7 +2543,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BCIO:010028</t>
+          <t>BCIO:010049</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2444,35 +2555,35 @@
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>secondary education teacher</t>
-        </is>
-      </c>
+      <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>midwifery associate professional</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>A teaching professional that teaches one or more subjects at secondary education level.</t>
-        </is>
-      </c>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A nursing and midwifery associate professional that provides basic health care and advice before, during and after pregnancy and childbirth. They implement care, treatment and referral plans usually established by medical, midwifery and other health professionals.</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>Assistant midwife, Traditional midwife</t>
         </is>
       </c>
       <c r="S57" t="inlineStr"/>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>Secondary school teacher, High school teacher</t>
-        </is>
-      </c>
+      <c r="T57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BCIO:010030</t>
+          <t>BCIO:010061</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2486,33 +2597,33 @@
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>early childhood educator</t>
+          <t>sport and fitness worker</t>
         </is>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>A teaching professional that promotes the social, physical, and intellectual development of children below primary school age through the provision of educational and play activities.</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A technician and associate professional that prepares for and competes in sporting events for financial gain, trains amateur and professional sportsmen and women to enhance performance, promotes participation and standards in sport, organises and officiates sporting events, or provides instruction, training and supervision for various forms of exercise and other recreational activities.</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>physical activity professional, exercise physiologist, exercise therapist, exercise specialist</t>
         </is>
       </c>
       <c r="S58" t="inlineStr"/>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>Early childhood educator, Pre-school teacher</t>
-        </is>
-      </c>
+      <c r="T58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BCIO:010007</t>
+          <t>BCIO:010063</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2523,36 +2634,36 @@
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>science and engineering professional</t>
-        </is>
-      </c>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>sports coach, instructor and official</t>
+        </is>
+      </c>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
-          <t>A professional that conducts research, improves or develops concepts, theories and operational methods or applies scientific knowledge.</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A sport and fitness worker that works with amateur and professional sportspersons to enhance performance and encourage greater participation in sport, and organizes and officiates in sporting events according to established rules.</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>Referee, Ski instructor, Sports coach, Sports official, Swimming instructor</t>
         </is>
       </c>
       <c r="S59" t="inlineStr"/>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>Science Professional, Mathematician, Actuary, Statistician, Life Science Professional, Engineering Professional, Electrotechnology Engineer, Architect, Planner, Surveyor, Designer</t>
-        </is>
-      </c>
+      <c r="T59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BCIO:010008</t>
+          <t>BCIO:010062</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2563,36 +2674,36 @@
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>health professional</t>
-        </is>
-      </c>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>athlete and sports player</t>
+        </is>
+      </c>
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>A professional that improves or develops concepts, theories and operational method, and applied scientific knowledge relating to medicine, nursing, dentistry, veterinary medicine, pharmacy, and promotion of health.</t>
-        </is>
-      </c>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A sport and fitness worker that participates in competitive sporting events. They train and compete, either individually or as part of a team, in their chosen sport.</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>Athlete, Bicycle racer, Boxer, Chess player , Footballer, Golfer, Hockey player, Jockey, Poker player, Racing driver, Skier, Tennis player, Wrestler</t>
         </is>
       </c>
       <c r="S60" t="inlineStr"/>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>Health professional; Arts therapist, Chiropractor, Dance and movement therapist, Occupational therapist, Osteopath, Podiatrist, Recreational therapist, Health staff, Clinic staff</t>
-        </is>
-      </c>
+      <c r="T60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BCIO:010013</t>
+          <t>BCIO:010064</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2604,35 +2715,35 @@
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>nursing professional</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>fitness and recreation instructor and programme leader</t>
+        </is>
+      </c>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t>A health professional that provides treatment, support and care services for people who are in need of nursing care due to the effects of ageing, injury, illness or other physical or mental impairment, or potential risks to health.</t>
-        </is>
-      </c>
-      <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A sport and fitness worker that leads, guides and instructs groups and individuals in recreational, fitness or outdoor adventure activities.</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>Aerobics instructor, Fitness instructor, Horse riding instructor, Outdoor adventure guide, Personal trainer, Sailing instructor, Underwater diving instructor</t>
         </is>
       </c>
       <c r="S61" t="inlineStr"/>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>Clinical nurse consultant, District nurse, Nurse anaesthetist, Nurse educator, Nurse practitioner, Operating theatre nurse, Professional nurse, Public health nurse, Specialist nurse, Nursing Counsellor, Study Nurse</t>
-        </is>
-      </c>
+      <c r="T61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BCIO:010022</t>
+          <t>BCIO:010059</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -2646,33 +2757,33 @@
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>dietician and nutritionist</t>
+          <t>social work associate professional</t>
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
-          <t>A health professional  that assesses, plans and implements programmes to enhance the impact of food and nutrition on human health.</t>
-        </is>
-      </c>
-      <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A technician and associate professional that implements social assistance programmes and community services and assist clients to deal with personal and social problems.</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>Community development worker, Community services worker, Crisis intervention worker, Disability services worker, Family services worker, Life skills instructor, Mental health support worker, Welfare support worker, Women’s shelter supervisor, Youth services worker</t>
         </is>
       </c>
       <c r="S62" t="inlineStr"/>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>Clinical dietician, Food service dietician, Nutritionist, Public health nutritionist, Sports nutritionist</t>
-        </is>
-      </c>
+      <c r="T62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BCIO:010014</t>
+          <t>BCIO:010057</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -2686,33 +2797,33 @@
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>midwifery professional</t>
+          <t>business and administration associate professional</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
-          <t>A health professional that plans, manages, provides and evaluates midwifery care services before, during and after pregnancy and childbirth. They provide delivery care for reducing health risks to women and newborn children, working autonomously or in teams with other health care providers.</t>
-        </is>
-      </c>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A technician and associate professional that performs mostly technical tasks connected with the practical application of knowledge relating to financial accounting and transaction matters, mathematical calculations, human resource development, selling and buying financial instruments, specialized secretarial tasks and enforcing or applying government rules.</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Financial and Mathematical associate professional, Sales and purchasing agent, Broker, Business Services Agent, Administrative and Specialized Secretary, Government regulatory associate professional, Medical secretary</t>
         </is>
       </c>
       <c r="S63" t="inlineStr"/>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>Midwife</t>
-        </is>
-      </c>
+      <c r="T63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BCIO:010015</t>
+          <t>BCIO:010060</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -2726,33 +2837,33 @@
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
-          <t>traditional and complementary medicine professional</t>
+          <t>religious associate professional</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t>A health professional that examines patients, prevents and treats illness, disease, injury and other physical and mental impairments and maintains general health in humans. They do this by applying knowledge, skills and practices acquired through extensive study of the theories, beliefs and experiences originating in specific cultures.</t>
-        </is>
-      </c>
-      <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A technician and associate professional that provides support to ministers of religion or to a religious community, undertake religious works, preach and propagate the teachings of a particular religion and endeavour to improve well-being through the power of faith and spiritual advice.</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>Faith healer, Lay preacher, Monk, Nun</t>
         </is>
       </c>
       <c r="S64" t="inlineStr"/>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>Acupuncturist, Ayurvedic practitioner,  Chinese herbal medicine practitioner, Homeopath, Naturopath, Unani practitioner</t>
-        </is>
-      </c>
+      <c r="T64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BCIO:010020</t>
+          <t>BCIO:010034</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -2763,36 +2874,32 @@
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>environmental and occupational health and hygiene professional</t>
-        </is>
-      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>legal, social and cultural professional</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
-          <t>A health professional that assesses, plans and implements programmes to recognize, monitor and control environmental factors that can potentially affect human health, to ensure safe and healthy working conditions and to prevent disease or injury caused by chemical, physical, radiological and biological agents or ergonomic factors.</t>
+          <t>A professional that conducts research, improves or develops concepts, theories and operational methods, or applies knowledge relating to the law, social or cultural studies.</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
       <c r="S65" t="inlineStr"/>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>Environmental health officer, Occupational health and safety adviser, Occupational hygienist, Radiation protection expert</t>
-        </is>
-      </c>
+      <c r="T65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BCIO:010017</t>
+          <t>BCIO:010037</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -2806,33 +2913,33 @@
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
-          <t>veterinarian</t>
+          <t>social professional</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
-          <t>A health professional that diagnoses, prevents and treats diseases, injuries and dysfunctions of animals.</t>
-        </is>
-      </c>
-      <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A legal, social and cultural professional that conducts research, improves or develops concepts, theories and operational methods or applies knowledge relating to psychology, sociology, philosophy, politics, economics, sociology, anthropology, history and other social sciences, or provides social services to meet the needs of individuals and families in a community.</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>Economist, Sociologist, Anthropologist, Philosopher, Historian, Political Scientist</t>
         </is>
       </c>
       <c r="S66" t="inlineStr"/>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>Animal pathologist, Veterinarian, Veterinary epidemiologist, Veterinary intern, Veterinary surgeon</t>
-        </is>
-      </c>
+      <c r="T66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BCIO:010021</t>
+          <t>BCIO:010039</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -2844,35 +2951,35 @@
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>physiotherapist</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>social work and counselling professional</t>
+        </is>
+      </c>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
-          <t>A health professional  that assesses, plans and implements rehabilitative programmes that improve or restore human motor functions, maximize movement ability, relieve pain syndromes, and treat or prevent physical challenges associated with injuries, diseases and other impairments.</t>
-        </is>
-      </c>
-      <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A social professional that provides advice and guidance to individuals, families, groups, communities and organizations in response to social and personal difficulties. They assist clients to develop skills and access resources and support services needed to respond to issues arising from unemployment, poverty, disability, addiction, criminal and delinquent behaviour, marital and other problems.</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>Counsellor, Addictions counsellor, Bereavement counsellor, Child and youth counsellor, District social welfare officer, Family counsellor, Marriage counsellor, Parole officer, Probation officer, Sexual assault counsellor, Social worker, Women’s welfare organizer</t>
         </is>
       </c>
       <c r="S67" t="inlineStr"/>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>Geriatric physical therapist, Manipulative therapist, Orthopaedic physical therapist, Paediatric physical therapist, Physical therapist, Physiotherapist</t>
-        </is>
-      </c>
+      <c r="T67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BCIO:010012</t>
+          <t>BCIO:010038</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -2884,22 +2991,26 @@
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>nursing and midwifery professional</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>psychologist</t>
+        </is>
+      </c>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
-          <t>A health professional that provides treatment and care services for people who are physically or mentally ill, disabled or infirm, and those with potential risks to health including before, during and after childbirth. They assume responsibility for the planning, management and evaluation of the care of patients, including the supervision of other health care workers, working autonomously or in teams with medical doctors and others in the practical application of preventive and curative measures.</t>
-        </is>
-      </c>
-      <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A social professional that studies the mental processes and behaviour of human beings as individuals or in groups, and applies this knowledge to promote personal, social, educational or occupational adjustment and development.</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>Clinical psychologist, Counselling psychologist, Educational psychologist, Forensic psychologist, Health psychologist, Neuropsychologist, Organizational psychologist, Psychotherapist, Sport and exercise psychologist</t>
         </is>
       </c>
       <c r="S68" t="inlineStr"/>
@@ -2908,7 +3019,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BCIO:010016</t>
+          <t>BCIO:010041</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -2922,33 +3033,33 @@
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
-          <t>paramedical practitioner</t>
+          <t>author and journalist</t>
         </is>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
-          <t>A health professional that provides advisory, diagnostic, curative and preventive medical services more limited in scope and complexity than those carried out by medical doctors. They work autonomously or with limited supervision of medical doctors, and apply advanced clinical procedures for treating and preventing diseases, injuries and other physical or mental impairments common to specific communities.</t>
-        </is>
-      </c>
-      <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A legal, social and cultural professional that conceives and creates literary works, and interprets and communicates news and public affairs through the media.</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>Author, Writer, Journalist, Translator, News anchor</t>
         </is>
       </c>
       <c r="S69" t="inlineStr"/>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>Advanced care paramedic, Clinical officer (paramedical), Feldscher, Primary care paramedic, Surgical technician</t>
-        </is>
-      </c>
+      <c r="T69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BCIO:010024</t>
+          <t>BCIO:010036</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -2962,33 +3073,33 @@
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
-          <t>optometrist and ophthalmic optician</t>
+          <t>librarian, archivist and curator</t>
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
-          <t>A health professional  that provides diagnosis, management and treatment services for disorders of the eyes and visual system.</t>
-        </is>
-      </c>
-      <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A legal, social and cultural professional that develops and maintains collections of archives, libraries, museums, art galleries and similar establishments.</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>Librarian, Archivist,  Curator</t>
         </is>
       </c>
       <c r="S70" t="inlineStr"/>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>Ophthalmic optician , Optometrist, Orthoptist</t>
-        </is>
-      </c>
+      <c r="T70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>BCIO:010023</t>
+          <t>BCIO:010035</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -3002,33 +3113,33 @@
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
-          <t>audiologist and speech therapist</t>
+          <t>legal professional</t>
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
-          <t>A health professional  that evaluates, manages and treats physical disorders affecting human hearing, speech, communication and swallowing.</t>
-        </is>
-      </c>
-      <c r="Q71" t="inlineStr"/>
-      <c r="R71" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A legal, social and cultural professional that conducts research on legal problems, advises clients on legal aspects of problems, pleads cases or conducts prosecutions in courts of law, presides over judicial proceedings in courts of law and draft laws and regulations.</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>Lawyer, Judge, Coroner</t>
         </is>
       </c>
       <c r="S71" t="inlineStr"/>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>Audiologist, Language therapist, Speech pathologist, Speech therapist</t>
-        </is>
-      </c>
+      <c r="T71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BCIO:010018</t>
+          <t>BCIO:010043</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -3042,33 +3153,33 @@
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
-          <t>dentist</t>
+          <t>creative and performing artist</t>
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
-          <t>A health professional that diagnoses treats and prevents diseases, injuries and abnormalities of the teeth, mouth, jaws and associated tissues by applying the principles and procedures of modern dentistry.</t>
-        </is>
-      </c>
-      <c r="Q72" t="inlineStr"/>
-      <c r="R72" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A legal, social and cultural professional that communicates ideas, impressions and facts in a wide range of media to achieve particular effects, interprets a composition such as a musical score or a script to perform or direct the performance, and hosts the presentation of such performance and other media events.</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>Visual artist, Musician, Singer, Composer, Dancer, Choreographer, Director, Producer, Actor, Announcer on radio, television and other media</t>
         </is>
       </c>
       <c r="S72" t="inlineStr"/>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>Dental practitioner, Dental surgeon, Dentist, Endodontist, Oral and maxillofacial surgeon, Oral pathologist, Orthodontist, Paedodontist, Periodontist, Prosthodontist, Stomatologist</t>
-        </is>
-      </c>
+      <c r="T72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BCIO:010009</t>
+          <t>BCIO:010042</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -3082,33 +3193,33 @@
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
-          <t>medical doctor</t>
+          <t>linguist</t>
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
-          <t>A health professional that studies, diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments in humans through the application of modern medicine. They plan, supervise and evaluate the implementation of care and treatment plans by other health care providers, and conduct medical education and research activities.</t>
-        </is>
-      </c>
-      <c r="Q73" t="inlineStr"/>
-      <c r="R73" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A legal, social and cultural professional that translates or interprets from one language into another.</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>Interpretator; other linguist</t>
         </is>
       </c>
       <c r="S73" t="inlineStr"/>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>District medical doctor-therapist, family medical practitioner, general practitioner, medical doctor (general), medical officer (general), physician (general), primary health care physician, resident medical officer specializing in general practice</t>
-        </is>
-      </c>
+      <c r="T73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>BCIO:010011</t>
+          <t>BCIO:010040</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -3120,35 +3231,35 @@
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>specialist medical practitioner</t>
-        </is>
-      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>religious professional</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
-          <t>A medical doctor that diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments in humans, using specialized testing, diagnostic, medical, surgical, physical and psychiatric techniques through application of the principles and procedures of modern medicine. They specialize in certain disease categories, types of patient or methods of treatment and may conduct medical education and research in their chosen areas of specialization.</t>
-        </is>
-      </c>
-      <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A legal, social and cultural professional that functions  as a perpetuator of sacred traditions, practices and beliefs. They conduct religious services, celebrate or administer the rites of a religious faith or denomination, provide spiritual and moral guidance and perform other functions associated with the practice of a religion.</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>Bonze, Imam, Minister of religion, Poojari, Priest, Rabbi</t>
         </is>
       </c>
       <c r="S74" t="inlineStr"/>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>Anaesthetist, Cardiologist, Emergency medicine specialist, Gynaecologist, Obstetrician, Ophthalmologist, Paediatrician, Pathologist, Preventive medicine specialist, Psychiatrist, Radiation oncologist, Radiologist, Resident medical officer in specialist training, Specialist medical practitioner (public health), Specialist physician (internal medicine), Specialist physician (nuclear medicine), Surgeon</t>
-        </is>
-      </c>
+      <c r="T74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BCIO:010010</t>
+          <t>BCIO:010025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -3159,36 +3270,36 @@
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>teaching professional</t>
+        </is>
+      </c>
       <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>generalist medical practitioner</t>
-        </is>
-      </c>
+      <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
-          <t>A medical doctor that diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments and maintains general health in humans through application of modern medicine. They do not limit their practice to certain disease categories or methods of treatment, and may assume responsibility for the provision of continuing and comprehensive medical care to individuals, families and communities.</t>
-        </is>
-      </c>
-      <c r="Q75" t="inlineStr"/>
-      <c r="R75" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A professional that teaches the theory and practice of one or more disciplines at different educational levels.</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>Education Methods Specialist, Other Language Teacher, Information Technology Teacher, Private Tutor, School Counsellor, Student Advisor</t>
         </is>
       </c>
       <c r="S75" t="inlineStr"/>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>Primary care physician, family doctor, GP</t>
-        </is>
-      </c>
+      <c r="T75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BCIO:010019</t>
+          <t>BCIO:010028</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -3202,33 +3313,33 @@
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
-          <t>pharmacist</t>
+          <t>secondary education teacher</t>
         </is>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
-          <t>A health professional that stores, preserves, compounds and dispenses medicinal products and counsel on the proper use and adverse effects of drugs and medicines following prescriptions issued by medical doctors and other health professionals.</t>
-        </is>
-      </c>
-      <c r="Q76" t="inlineStr"/>
-      <c r="R76" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A teaching professional that teaches one or more subjects at secondary education level.</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>Secondary school teacher, High school teacher</t>
         </is>
       </c>
       <c r="S76" t="inlineStr"/>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>Dispensing chemist, Hospital pharmacist, Industrial pharmacist, Retail pharmacist</t>
-        </is>
-      </c>
+      <c r="T76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BCIO:010044</t>
+          <t>BCIO:010026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -3239,23 +3350,27 @@
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>technician and associate professional</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>university and higher education teacher</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr">
         <is>
-          <t>A professional that performs technical and related tasks connected with research and the application of scientific or artistic concepts and operational methods, and government or business regulations.</t>
-        </is>
-      </c>
-      <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A teaching professional that prepares and delivers lectures and conduct tutorials in one or more subjects within a prescribed course of study at a university or other higher educational institution. They conduct research, and prepare scholarly papers and books.</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>Higher education lecturer, Professor, University lecturer, University tutor</t>
         </is>
       </c>
       <c r="S77" t="inlineStr"/>
@@ -3264,7 +3379,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>BCIO:010045</t>
+          <t>BCIO:010031</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -3278,33 +3393,33 @@
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
-          <t>health associate professional</t>
+          <t>special needs teacher</t>
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr">
         <is>
-          <t>A technician and associate professional that performs technical and practical tasks to support diagnosis and treatment of illness, disease, injuries and impairments in humans or animals, and supports the implementation of health care usually established by medical, veterinary, nursing and other health professionals.</t>
-        </is>
-      </c>
-      <c r="Q78" t="inlineStr"/>
-      <c r="R78" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A teaching professional that teaches children, young persons or adults with physical or intellectual special needs.</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>Learning disabilities special education teacher, Learning support teacher, Remedial teacher, Teacher of gifted children, Teacher of the hearing impaired, Teacher of the sight impaired</t>
         </is>
       </c>
       <c r="S78" t="inlineStr"/>
-      <c r="T78" t="inlineStr">
-        <is>
-          <t>Veterinary Technician</t>
-        </is>
-      </c>
+      <c r="T78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BCIO:010047</t>
+          <t>BCIO:010027</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -3316,35 +3431,35 @@
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>nursing and midwifery associate professional</t>
-        </is>
-      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>vocational education teacher</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr">
         <is>
-          <t>A health associate professional that provides basic nursing and personal care for people who are physically or mentally ill, disabled or infirm, and for others in need of care due to potential risks to health including before, during and after childbirth. They generally work under the supervision of, and in support of, implementation of health care, treatment and referrals plans established by medical, nursing, midwifery and other health professionals.</t>
-        </is>
-      </c>
-      <c r="Q79" t="inlineStr"/>
-      <c r="R79" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A teaching professional that teaches or instructs vocational or occupational subjects in adult and further education institutions and to senior students in secondary schools and colleges.</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>Automotive technology instructor, Cosmetology instructor, Vocational education teacher</t>
         </is>
       </c>
       <c r="S79" t="inlineStr"/>
-      <c r="T79" t="inlineStr">
-        <is>
-          <t>Practice assistant, Quit Smoking Counsellor, Health educator, Dispensing Optician, Information Technician</t>
-        </is>
-      </c>
+      <c r="T79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>BCIO:010049</t>
+          <t>BCIO:010033</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -3356,35 +3471,35 @@
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>arts teacher</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>midwifery associate professional</t>
-        </is>
-      </c>
+      <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr">
         <is>
-          <t>A nursing and midwifery associate professional that provides basic health care and advice before, during and after pregnancy and childbirth. They implement care, treatment and referral plans usually established by medical, midwifery and other health professionals.</t>
-        </is>
-      </c>
-      <c r="Q80" t="inlineStr"/>
-      <c r="R80" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A teaching professional  that teaches students in the practice, theory and performance of dance, drama, visual and other arts (excluding music) in private or small group tuition or within mainstream educational institutions.</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>Dance teacher (private tuition), Drama teacher (private tuition), Painting teacher (private tuition), Sculpture teacher (private tuition)</t>
         </is>
       </c>
       <c r="S80" t="inlineStr"/>
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>Assistant midwife, Traditional midwife</t>
-        </is>
-      </c>
+      <c r="T80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BCIO:010048</t>
+          <t>BCIO:010029</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -3396,35 +3511,31 @@
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>primary school teacher</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>nursing associate professional</t>
-        </is>
-      </c>
+      <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr">
         <is>
-          <t>A nursing and midwifery associate professional that provides basic nursing and personal care for people in need of such care due to effects of ageing, illness, injury, or other physical or mental impairment. They generally work under the supervision of, and in support of, implementation of health care, treatment and referrals plans established by medical, nursing and other health professionals.</t>
+          <t>A teaching professional that teaches teach a range of subjects at the primary education level.</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
       <c r="S81" t="inlineStr"/>
-      <c r="T81" t="inlineStr">
-        <is>
-          <t>Assistant nurse, Associate professional nurse, Enrolled nurse, Practical nurse</t>
-        </is>
-      </c>
+      <c r="T81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BCIO:010055</t>
+          <t>BCIO:010032</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -3436,36 +3547,35 @@
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>environmental and occupational health inspector and associate</t>
-        </is>
-      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>music teacher</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr">
         <is>
-          <t>A health associate professional that investigates the implementation of rules and regulations relating to environmental factors that may affect human health, safety in the 
-workplace, and safety of processes for the production of goods and services. They may implement and evaluate programmes to restore or improve safety and sanitary conditions under the supervision of a health professional.</t>
-        </is>
-      </c>
-      <c r="Q82" t="inlineStr"/>
-      <c r="R82" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A teaching professional that teaches students in the practice, theory and performance of music in private or small group tuition or within mainstream educational institutions.</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>Guitar teacher (private tuition), Piano teacher (private tuition), Singing teacher (private tuition), Violin teacher (private tuition)</t>
         </is>
       </c>
       <c r="S82" t="inlineStr"/>
-      <c r="T82" t="inlineStr">
-        <is>
-          <t>Food sanitation and safety inspector, Health inspector, Occupational health and safety inspector, Pollution inspector, Product safety inspector, Sanitarian, Sanitary inspector</t>
-        </is>
-      </c>
+      <c r="T82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BCIO:010051</t>
+          <t>BCIO:010030</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -3477,35 +3587,35 @@
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>dental assistant and therapist</t>
-        </is>
-      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>early childhood educator</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr">
         <is>
-          <t>A health associate professional that provides basic dental care services for the prevention and treatment of diseases and disorders of the teeth and mouth, according to care plans and procedures established by a dentist or other oral health professional.</t>
-        </is>
-      </c>
-      <c r="Q83" t="inlineStr"/>
-      <c r="R83" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A teaching professional that promotes the social, physical, and intellectual development of children below primary school age through the provision of educational and play activities.</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>Early childhood educator, Pre-school teacher</t>
         </is>
       </c>
       <c r="S83" t="inlineStr"/>
-      <c r="T83" t="inlineStr">
-        <is>
-          <t>Dental assistant, Dental hygienist , Dental therapist</t>
-        </is>
-      </c>
+      <c r="T83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BCIO:010054</t>
+          <t>BCIO:010007</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -3516,36 +3626,36 @@
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>science and engineering professional</t>
+        </is>
+      </c>
       <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>medical assistant</t>
-        </is>
-      </c>
+      <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr">
         <is>
-          <t>A health associate professional that performs basic clinical and administrative tasks to support patient care under the direct supervision of a medical practitioner or other health professional.</t>
-        </is>
-      </c>
-      <c r="Q84" t="inlineStr"/>
-      <c r="R84" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A professional that conducts research, improves or develops concepts, theories and operational methods or applies scientific knowledge.</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>Science Professional, Mathematician, Actuary, Statistician, Life Science Professional, Engineering Professional, Electrotechnology Engineer, Architect, Planner, Surveyor, Designer</t>
         </is>
       </c>
       <c r="S84" t="inlineStr"/>
-      <c r="T84" t="inlineStr">
-        <is>
-          <t>Clinical assistant, Medical assistant, Ophthalmic assistant</t>
-        </is>
-      </c>
+      <c r="T84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BCIO:010053</t>
+          <t>BCIO:010008</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -3556,36 +3666,36 @@
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>health professional</t>
+        </is>
+      </c>
       <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>physiotherapy technician and assistant</t>
-        </is>
-      </c>
+      <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr">
         <is>
-          <t>A health associate professional that provides physical therapeutic treatments to patients in circumstances where functional movement is threatened by injury, disease or impairment. Therapies are usually provided according to rehabilitative plans established by a physiotherapist or other health professional.</t>
-        </is>
-      </c>
-      <c r="Q85" t="inlineStr"/>
-      <c r="R85" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A professional that improves or develops concepts, theories and operational method, and applied scientific knowledge relating to medicine, nursing, dentistry, veterinary medicine, pharmacy, and promotion of health.</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>Health professional; Arts therapist, Chiropractor, Dance and movement therapist, Occupational therapist, Osteopath, Podiatrist, Recreational therapist, Health staff, Clinic staff</t>
         </is>
       </c>
       <c r="S85" t="inlineStr"/>
-      <c r="T85" t="inlineStr">
-        <is>
-          <t>Acupressure therapist, Electrotherapist, Hydrotherapist, Massage therapist, Physical rehabilitation technician, Physiotherapy technician, Shiatsu therapist</t>
-        </is>
-      </c>
+      <c r="T85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BCIO:010050</t>
+          <t>BCIO:010021</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -3597,35 +3707,35 @@
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>traditional and complementary medicine associate professional</t>
-        </is>
-      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>physiotherapist</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr">
         <is>
-          <t>A health associate professional that prevents and treats human physical and mental illnesses, disorders and injuries using herbal and other therapies based on theories, beliefs and experiences originating in specific cultures. They administer treatments using traditional techniques and medicaments, either acting independently or according to therapeutic care plans established by a traditional medicine or other health professional.</t>
-        </is>
-      </c>
-      <c r="Q86" t="inlineStr"/>
-      <c r="R86" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A health professional  that assesses, plans and implements rehabilitative programmes that improve or restore human motor functions, maximize movement ability, relieve pain syndromes, and treat or prevent physical challenges associated with injuries, diseases and other impairments.</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>Geriatric physical therapist, Manipulative therapist, Orthopaedic physical therapist, Paediatric physical therapist, Physical therapist, Physiotherapist</t>
         </is>
       </c>
       <c r="S86" t="inlineStr"/>
-      <c r="T86" t="inlineStr">
-        <is>
-          <t>Acupuncture technician, Ayurvedic technician, Bonesetter, Herbalist , Homeopathy technician, Scraping and cupping therapist, Village healer, Witch doctor</t>
-        </is>
-      </c>
+      <c r="T86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>BCIO:010052</t>
+          <t>BCIO:010018</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -3637,35 +3747,35 @@
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>community health worker</t>
-        </is>
-      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>dentist</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr">
         <is>
-          <t>A health associate professional that provides health education, referral and follow-up, case management, basic preventive health care and home visiting services to specific communities. They provide support and assistance to individuals and families in navigating the health and social services system.</t>
-        </is>
-      </c>
-      <c r="Q87" t="inlineStr"/>
-      <c r="R87" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A health professional that diagnoses treats and prevents diseases, injuries and abnormalities of the teeth, mouth, jaws and associated tissues by applying the principles and procedures of modern dentistry.</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>Dental practitioner, Dental surgeon, Dentist, Endodontist, Oral and maxillofacial surgeon, Oral pathologist, Orthodontist, Paedodontist, Periodontist, Prosthodontist, Stomatologist</t>
         </is>
       </c>
       <c r="S87" t="inlineStr"/>
-      <c r="T87" t="inlineStr">
-        <is>
-          <t>Community health aide, Community health promoter, Community health worker, Village health worker, outreach worker, health worker</t>
-        </is>
-      </c>
+      <c r="T87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>BCIO:010056</t>
+          <t>BCIO:010022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -3677,35 +3787,35 @@
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>ambulance worker</t>
-        </is>
-      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>dietician and nutritionist</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr">
         <is>
-          <t>A health associate professional that provides emergency health care to patients who are injured, sick, infirm or otherwise physically or mentally impaired prior to and during transport to medical facilities.</t>
-        </is>
-      </c>
-      <c r="Q88" t="inlineStr"/>
-      <c r="R88" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A health professional  that assesses, plans and implements programmes to enhance the impact of food and nutrition on human health.</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>Clinical dietician, Food service dietician, Nutritionist, Public health nutritionist, Sports nutritionist</t>
         </is>
       </c>
       <c r="S88" t="inlineStr"/>
-      <c r="T88" t="inlineStr">
-        <is>
-          <t>Ambulance officer, Ambulance paramedic, Emergency medical technician, Emergency paramedic</t>
-        </is>
-      </c>
+      <c r="T88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>BCIO:010046</t>
+          <t>BCIO:010020</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -3717,35 +3827,35 @@
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>medical and pharmaceutical technician</t>
-        </is>
-      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>environmental and occupational health and hygiene professional</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr">
         <is>
-          <t>A health associate professional that performs technical tasks to assist in diagnosis and treatment of illness, disease, injuries and impairments.</t>
-        </is>
-      </c>
-      <c r="Q89" t="inlineStr"/>
-      <c r="R89" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A health professional that assesses, plans and implements programmes to recognize, monitor and control environmental factors that can potentially affect human health, to ensure safe and healthy working conditions and to prevent disease or injury caused by chemical, physical, radiological and biological agents or ergonomic factors.</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>Environmental health officer, Occupational health and safety adviser, Occupational hygienist, Radiation protection expert</t>
         </is>
       </c>
       <c r="S89" t="inlineStr"/>
-      <c r="T89" t="inlineStr">
-        <is>
-          <t>Medical imaging and therapeutic equipment technician, Medical and Pathology laboratory technician, Pharmaceutical technician, Medical and dental prosthetic technician</t>
-        </is>
-      </c>
+      <c r="T89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>BCIO:010057</t>
+          <t>BCIO:010009</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -3759,33 +3869,33 @@
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
-          <t>business and administration associate professional</t>
+          <t>medical doctor</t>
         </is>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr">
         <is>
-          <t>A technician and associate professional that performs mostly technical tasks connected with the practical application of knowledge relating to financial accounting and transaction matters, mathematical calculations, human resource development, selling and buying financial instruments, specialized secretarial tasks and enforcing or applying government rules.</t>
-        </is>
-      </c>
-      <c r="Q90" t="inlineStr"/>
-      <c r="R90" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A health professional that studies, diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments in humans through the application of modern medicine. They plan, supervise and evaluate the implementation of care and treatment plans by other health care providers, and conduct medical education and research activities.</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>District medical doctor-therapist, family medical practitioner, general practitioner, medical doctor (general), medical officer (general), physician (general), primary health care physician, resident medical officer specializing in general practice</t>
         </is>
       </c>
       <c r="S90" t="inlineStr"/>
-      <c r="T90" t="inlineStr">
-        <is>
-          <t>Financial and Mathematical associate professional, Sales and purchasing agent, Broker, Business Services Agent, Administrative and Specialized Secretary, Government regulatory associate professional, Medical secretary</t>
-        </is>
-      </c>
+      <c r="T90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>BCIO:010059</t>
+          <t>BCIO:010011</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -3797,35 +3907,35 @@
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>social work associate professional</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>specialist medical practitioner</t>
+        </is>
+      </c>
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr">
         <is>
-          <t>A technician and associate professional that implements social assistance programmes and community services and assist clients to deal with personal and social problems.</t>
-        </is>
-      </c>
-      <c r="Q91" t="inlineStr"/>
-      <c r="R91" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A medical doctor that diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments in humans, using specialized testing, diagnostic, medical, surgical, physical and psychiatric techniques through application of the principles and procedures of modern medicine. They specialize in certain disease categories, types of patient or methods of treatment and may conduct medical education and research in their chosen areas of specialization.</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>Anaesthetist, Cardiologist, Emergency medicine specialist, Gynaecologist, Obstetrician, Ophthalmologist, Paediatrician, Pathologist, Preventive medicine specialist, Psychiatrist, Radiation oncologist, Radiologist, Resident medical officer in specialist training, Specialist medical practitioner (public health), Specialist physician (internal medicine), Specialist physician (nuclear medicine), Surgeon</t>
         </is>
       </c>
       <c r="S91" t="inlineStr"/>
-      <c r="T91" t="inlineStr">
-        <is>
-          <t>Community development worker, Community services worker, Crisis intervention worker, Disability services worker, Family services worker, Life skills instructor, Mental health support worker, Welfare support worker, Women’s shelter supervisor, Youth services worker</t>
-        </is>
-      </c>
+      <c r="T91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>BCIO:010058</t>
+          <t>BCIO:010010</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -3837,35 +3947,35 @@
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>legal and related associate professional</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>generalist medical practitioner</t>
+        </is>
+      </c>
       <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr">
         <is>
-          <t>A technician and associate professional that performs support functions in courts of law or in law offices, provide services related to such legal matters as insurance contracts, the transferring of property and the granting of loans and other financial transactions, or conduct investigations for clients.</t>
-        </is>
-      </c>
-      <c r="Q92" t="inlineStr"/>
-      <c r="R92" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A medical doctor that diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments and maintains general health in humans through application of modern medicine. They do not limit their practice to certain disease categories or methods of treatment, and may assume responsibility for the provision of continuing and comprehensive medical care to individuals, families and communities.</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>Primary care physician, family doctor, GP</t>
         </is>
       </c>
       <c r="S92" t="inlineStr"/>
-      <c r="T92" t="inlineStr">
-        <is>
-          <t>Bailiff, Judge’s clerk, Conveyancing clerk, Court clerk, Justice of the peace, Law clerk, Legal assistant, Paralegal, Private detective, Title searcher</t>
-        </is>
-      </c>
+      <c r="T92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BCIO:010065</t>
+          <t>BCIO:010023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -3879,33 +3989,33 @@
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
-          <t>artistic, cultural and culinary associate professional</t>
+          <t>audiologist and speech therapist</t>
         </is>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr">
         <is>
-          <t>A technician and associate professional that combines creative skills and technical and cultural knowledge in creative media or food.</t>
-        </is>
-      </c>
-      <c r="Q93" t="inlineStr"/>
-      <c r="R93" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A health professional  that evaluates, manages and treats physical disorders affecting human hearing, speech, communication and swallowing.</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>Audiologist, Language therapist, Speech pathologist, Speech therapist</t>
         </is>
       </c>
       <c r="S93" t="inlineStr"/>
-      <c r="T93" t="inlineStr">
-        <is>
-          <t>Photographer, Interior designers and decorator, Gallery, museum and library technician, Chef</t>
-        </is>
-      </c>
+      <c r="T93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BCIO:010060</t>
+          <t>BCIO:010014</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
@@ -3919,33 +4029,33 @@
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
-          <t>religious associate professional</t>
+          <t>midwifery professional</t>
         </is>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr">
         <is>
-          <t>A technician and associate professional that provides support to ministers of religion or to a religious community, undertake religious works, preach and propagate the teachings of a particular religion and endeavour to improve well-being through the power of faith and spiritual advice.</t>
-        </is>
-      </c>
-      <c r="Q94" t="inlineStr"/>
-      <c r="R94" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A health professional that plans, manages, provides and evaluates midwifery care services before, during and after pregnancy and childbirth. They provide delivery care for reducing health risks to women and newborn children, working autonomously or in teams with other health care providers.</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>Midwife</t>
         </is>
       </c>
       <c r="S94" t="inlineStr"/>
-      <c r="T94" t="inlineStr">
-        <is>
-          <t>Faith healer, Lay preacher, Monk, Nun</t>
-        </is>
-      </c>
+      <c r="T94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>BCIO:010066</t>
+          <t>BCIO:010015</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -3959,33 +4069,33 @@
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
         <is>
-          <t>information and communications technician</t>
+          <t>traditional and complementary medicine professional</t>
         </is>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr">
         <is>
-          <t>A technician and associate professional that provides support for the day to day running of computer systems, communication systems and networks, broadcast images and sound, telecommunication signals on land, sea or in aircraft.</t>
-        </is>
-      </c>
-      <c r="Q95" t="inlineStr"/>
-      <c r="R95" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A health professional that examines patients, prevents and treats illness, disease, injury and other physical and mental impairments and maintains general health in humans. They do this by applying knowledge, skills and practices acquired through extensive study of the theories, beliefs and experiences originating in specific cultures.</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>Acupuncturist, Ayurvedic practitioner,  Chinese herbal medicine practitioner, Homeopath, Naturopath, Unani practitioner</t>
         </is>
       </c>
       <c r="S95" t="inlineStr"/>
-      <c r="T95" t="inlineStr">
-        <is>
-          <t>Information and Communications Technology Operations and User Support Technician, Telecommunications and Broadcasting Technician</t>
-        </is>
-      </c>
+      <c r="T95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>BCIO:010061</t>
+          <t>BCIO:010017</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -3999,33 +4109,33 @@
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
-          <t>sport and fitness worker</t>
+          <t>veterinarian</t>
         </is>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr">
         <is>
-          <t>A technician and associate professional that prepares for and competes in sporting events for financial gain, trains amateur and professional sportsmen and women to enhance performance, promotes participation and standards in sport, organises and officiates sporting events, or provides instruction, training and supervision for various forms of exercise and other recreational activities.</t>
-        </is>
-      </c>
-      <c r="Q96" t="inlineStr"/>
-      <c r="R96" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A health professional that diagnoses, prevents and treats diseases, injuries and dysfunctions of animals.</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>Animal pathologist, Veterinarian, Veterinary epidemiologist, Veterinary intern, Veterinary surgeon</t>
         </is>
       </c>
       <c r="S96" t="inlineStr"/>
-      <c r="T96" t="inlineStr">
-        <is>
-          <t>physical activity professional, exercise physiologist, exercise therapist, exercise specialist</t>
-        </is>
-      </c>
+      <c r="T96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>BCIO:010064</t>
+          <t>BCIO:010013</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -4037,35 +4147,35 @@
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>fitness and recreation instructor and programme leader</t>
-        </is>
-      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>nursing professional</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr">
         <is>
-          <t>A sport and fitness worker that leads, guides and instructs groups and individuals in recreational, fitness or outdoor adventure activities.</t>
-        </is>
-      </c>
-      <c r="Q97" t="inlineStr"/>
-      <c r="R97" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A health professional that provides treatment, support and care services for people who are in need of nursing care due to the effects of ageing, injury, illness or other physical or mental impairment, or potential risks to health.</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>Clinical nurse consultant, District nurse, Nurse anaesthetist, Nurse educator, Nurse practitioner, Operating theatre nurse, Professional nurse, Public health nurse, Specialist nurse, Nursing Counsellor, Study Nurse</t>
         </is>
       </c>
       <c r="S97" t="inlineStr"/>
-      <c r="T97" t="inlineStr">
-        <is>
-          <t>Aerobics instructor, Fitness instructor, Horse riding instructor, Outdoor adventure guide, Personal trainer, Sailing instructor, Underwater diving instructor</t>
-        </is>
-      </c>
+      <c r="T97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>BCIO:010063</t>
+          <t>BCIO:010016</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -4077,35 +4187,35 @@
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>sports coach, instructor and official</t>
-        </is>
-      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>paramedical practitioner</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr">
         <is>
-          <t>A sport and fitness worker that works with amateur and professional sportspersons to enhance performance and encourage greater participation in sport, and organizes and officiates in sporting events according to established rules.</t>
-        </is>
-      </c>
-      <c r="Q98" t="inlineStr"/>
-      <c r="R98" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A health professional that provides advisory, diagnostic, curative and preventive medical services more limited in scope and complexity than those carried out by medical doctors. They work autonomously or with limited supervision of medical doctors, and apply advanced clinical procedures for treating and preventing diseases, injuries and other physical or mental impairments common to specific communities.</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>Advanced care paramedic, Clinical officer (paramedical), Feldscher, Primary care paramedic, Surgical technician</t>
         </is>
       </c>
       <c r="S98" t="inlineStr"/>
-      <c r="T98" t="inlineStr">
-        <is>
-          <t>Referee, Ski instructor, Sports coach, Sports official, Swimming instructor</t>
-        </is>
-      </c>
+      <c r="T98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>BCIO:010062</t>
+          <t>BCIO:010024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -4117,35 +4227,35 @@
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>athlete and sports player</t>
-        </is>
-      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>optometrist and ophthalmic optician</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr">
         <is>
-          <t>A sport and fitness worker that participates in competitive sporting events. They train and compete, either individually or as part of a team, in their chosen sport.</t>
-        </is>
-      </c>
-      <c r="Q99" t="inlineStr"/>
-      <c r="R99" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A health professional  that provides diagnosis, management and treatment services for disorders of the eyes and visual system.</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>Ophthalmic optician , Optometrist, Orthoptist</t>
         </is>
       </c>
       <c r="S99" t="inlineStr"/>
-      <c r="T99" t="inlineStr">
-        <is>
-          <t>Athlete, Bicycle racer, Boxer, Chess player , Footballer, Golfer, Hockey player, Jockey, Poker player, Racing driver, Skier, Tennis player, Wrestler</t>
-        </is>
-      </c>
+      <c r="T99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>BCIO:010034</t>
+          <t>BCIO:010012</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -4156,32 +4266,32 @@
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>legal, social and cultural professional</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>nursing and midwifery professional</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr">
         <is>
-          <t>A professional that conducts research, improves or develops concepts, theories and operational methods, or applies knowledge relating to the law, social or cultural studies.</t>
+          <t>A health professional that provides treatment and care services for people who are physically or mentally ill, disabled or infirm, and those with potential risks to health including before, during and after childbirth. They assume responsibility for the planning, management and evaluation of the care of patients, including the supervision of other health care workers, working autonomously or in teams with medical doctors and others in the practical application of preventive and curative measures.</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr"/>
-      <c r="R100" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
       <c r="S100" t="inlineStr"/>
       <c r="T100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>BCIO:010041</t>
+          <t>BCIO:010019</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -4195,33 +4305,33 @@
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr">
         <is>
-          <t>author and journalist</t>
+          <t>pharmacist</t>
         </is>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that conceives and creates literary works, and interprets and communicates news and public affairs through the media.</t>
-        </is>
-      </c>
-      <c r="Q101" t="inlineStr"/>
-      <c r="R101" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A health professional that stores, preserves, compounds and dispenses medicinal products and counsel on the proper use and adverse effects of drugs and medicines following prescriptions issued by medical doctors and other health professionals.</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>Dispensing chemist, Hospital pharmacist, Industrial pharmacist, Retail pharmacist</t>
         </is>
       </c>
       <c r="S101" t="inlineStr"/>
-      <c r="T101" t="inlineStr">
-        <is>
-          <t>Author, Writer, Journalist, Translator, News anchor</t>
-        </is>
-      </c>
+      <c r="T101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>BCIO:010036</t>
+          <t>BCIO:010083</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -4231,37 +4341,37 @@
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>researcher role</t>
+        </is>
+      </c>
       <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>librarian, archivist and curator</t>
-        </is>
-      </c>
+      <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that develops and maintains collections of archives, libraries, museums, art galleries and similar establishments.</t>
-        </is>
-      </c>
-      <c r="Q102" t="inlineStr"/>
-      <c r="R102" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A occupational role played by a person that contributes substantively to production or reporting of a research study.</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>researcher, research assistant, investigator</t>
         </is>
       </c>
       <c r="S102" t="inlineStr"/>
-      <c r="T102" t="inlineStr">
-        <is>
-          <t>Librarian, Archivist,  Curator</t>
-        </is>
-      </c>
+      <c r="T102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>BCIO:010037</t>
+          <t>BCIO:030000</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
@@ -4272,36 +4382,27 @@
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>social professional</t>
-        </is>
-      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>behaviour change intervention study investigator role</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that conducts research, improves or develops concepts, theories and operational methods or applies knowledge relating to psychology, sociology, philosophy, politics, economics, sociology, anthropology, history and other social sciences, or provides social services to meet the needs of individuals and families in a community.</t>
+          <t>A researcher role played by a person that contributes substantively to production or reporting of a BCI evaluation study.</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr"/>
-      <c r="R103" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
       <c r="S103" t="inlineStr"/>
-      <c r="T103" t="inlineStr">
-        <is>
-          <t>Economist, Sociologist, Anthropologist, Philosopher, Historian, Political Scientist</t>
-        </is>
-      </c>
+      <c r="T103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>BCIO:010038</t>
+          <t>BCIO:010077</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
@@ -4311,37 +4412,37 @@
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>skilled agricultural, forestry and fishery worker</t>
+        </is>
+      </c>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t>psychologist</t>
-        </is>
-      </c>
+      <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr">
         <is>
-          <t>A social professional that studies the mental processes and behaviour of human beings as individuals or in groups, and applies this knowledge to promote personal, social, educational or occupational adjustment and development.</t>
-        </is>
-      </c>
-      <c r="Q104" t="inlineStr"/>
-      <c r="R104" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>An occupational role that grows and harvests plants or animals to provide food, shelter and income for themselves and their households.</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>Market gardener, Crop grower, Animal Producer, Mixed Crop and Animal Producer, Forestry worker, Fishery worker, Hunter. Subsistence Crop Farmer, Subsistence Livestock Farmer</t>
         </is>
       </c>
       <c r="S104" t="inlineStr"/>
-      <c r="T104" t="inlineStr">
-        <is>
-          <t>Clinical psychologist, Counselling psychologist, Educational psychologist, Forensic psychologist, Health psychologist, Neuropsychologist, Organizational psychologist, Psychotherapist, Sport and exercise psychologist</t>
-        </is>
-      </c>
+      <c r="T104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>BCIO:010039</t>
+          <t>BCIO:010080</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
@@ -4351,37 +4452,33 @@
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>assembler</t>
+        </is>
+      </c>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>social work and counselling professional</t>
-        </is>
-      </c>
+      <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr">
         <is>
-          <t>A social professional that provides advice and guidance to individuals, families, groups, communities and organizations in response to social and personal difficulties. They assist clients to develop skills and access resources and support services needed to respond to issues arising from unemployment, poverty, disability, addiction, criminal and delinquent behaviour, marital and other problems.</t>
+          <t>An occupational role that assembles products from component parts according to strict specifications and procedures.</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr"/>
-      <c r="R105" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
       <c r="S105" t="inlineStr"/>
-      <c r="T105" t="inlineStr">
-        <is>
-          <t>Counsellor, Addictions counsellor, Bereavement counsellor, Child and youth counsellor, District social welfare officer, Family counsellor, Marriage counsellor, Parole officer, Probation officer, Sexual assault counsellor, Social worker, Women’s welfare organizer</t>
-        </is>
-      </c>
+      <c r="T105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>BCIO:010042</t>
+          <t>BCIO:010078</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
@@ -4391,37 +4488,37 @@
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>craft and related trades worker</t>
+        </is>
+      </c>
       <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>linguist</t>
-        </is>
-      </c>
+      <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that translates or interprets from one language into another.</t>
-        </is>
-      </c>
-      <c r="Q106" t="inlineStr"/>
-      <c r="R106" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>An occupational role that applies specific technical and practical knowledge and skills to construct and maintain buildings, machinery, equipment or tools, carries out printing work, and produces or processes foodstuffs, textiles and wooden, metal and other articles, including handicraft goods.</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>Building Trade Worker, Metal Workers, Machinery Worker, Handicraft Worker, Printing Worker, Electrical Equipment Installers and Repairer, Electronics and Telecommunications Installer and Repairer, Food Processing Worker, Woodworker, Tobacco Product Maker</t>
         </is>
       </c>
       <c r="S106" t="inlineStr"/>
-      <c r="T106" t="inlineStr">
-        <is>
-          <t>Interpretator; other linguist</t>
-        </is>
-      </c>
+      <c r="T106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>BCIO:010035</t>
+          <t>BCIO:010000</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -4429,39 +4526,35 @@
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>behaviour change intervention source</t>
+        </is>
+      </c>
       <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>legal professional</t>
-        </is>
-      </c>
+      <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that conducts research on legal problems, advises clients on legal aspects of problems, pleads cases or conducts prosecutions in courts of law, presides over judicial proceedings in courts of law and draft laws and regulations.</t>
+          <t>A role played by a person, population or organisation that provides a BCI.</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr"/>
-      <c r="R107" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
       <c r="S107" t="inlineStr"/>
-      <c r="T107" t="inlineStr">
-        <is>
-          <t>Lawyer, Judge, Coroner</t>
-        </is>
-      </c>
+      <c r="T107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>BCIO:010043</t>
+          <t>BCIO:010138</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -4470,38 +4563,34 @@
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>organisational source role</t>
+        </is>
+      </c>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>creative and performing artist</t>
-        </is>
-      </c>
+      <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that communicates ideas, impressions and facts in a wide range of media to achieve particular effects, interprets a composition such as a musical score or a script to perform or direct the performance, and hosts the presentation of such performance and other media events.</t>
+          <t>A BCI source role that is borne by an organisation.</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr"/>
-      <c r="R108" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
       <c r="S108" t="inlineStr"/>
-      <c r="T108" t="inlineStr">
-        <is>
-          <t>Visual artist, Musician, Singer, Composer, Dancer, Choreographer, Director, Producer, Actor, Announcer on radio, television and other media</t>
-        </is>
-      </c>
+      <c r="T108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>BCIO:010040</t>
+          <t>BCIO:010001</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -4510,38 +4599,34 @@
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>person source role</t>
+        </is>
+      </c>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>religious professional</t>
-        </is>
-      </c>
+      <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that functions  as a perpetuator of sacred traditions, practices and beliefs. They conduct religious services, celebrate or administer the rites of a religious faith or denomination, provide spiritual and moral guidance and perform other functions associated with the practice of a religion.</t>
+          <t>A behaviour change intervention source role that inheres in a person.</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr"/>
-      <c r="R109" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
       <c r="S109" t="inlineStr"/>
-      <c r="T109" t="inlineStr">
-        <is>
-          <t>Bonze, Imam, Minister of religion, Poojari, Priest, Rabbi</t>
-        </is>
-      </c>
+      <c r="T109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>BCIO:010081</t>
+          <t>BCIO:010134</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
@@ -4550,38 +4635,34 @@
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>elementary occupation</t>
-        </is>
-      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>source involved in development of intervention</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr">
         <is>
-          <t>An occupational role that involves the performance of simple and routine tasks which may require the use of hand-held tools and considerable physical effort.</t>
+          <t>A BCI source that is involved in the development of intervention content.</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr"/>
-      <c r="R110" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
       <c r="S110" t="inlineStr"/>
-      <c r="T110" t="inlineStr">
-        <is>
-          <t>Cleaner, Labourer, Food Preparation Assistant, Street and Related Services Worker, Street Vendor (excluding Food), Refuse Worker</t>
-        </is>
-      </c>
+      <c r="T110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>BCIO:010080</t>
+          <t>BCIO:010135</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -4593,7 +4674,7 @@
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
-          <t>assembler</t>
+          <t>source involved in co-production of intervention</t>
         </is>
       </c>
       <c r="J111" t="inlineStr"/>
@@ -4602,22 +4683,22 @@
       <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr">
         <is>
-          <t>An occupational role that assembles products from component parts according to strict specifications and procedures.</t>
+          <t>A source involved in development of intervention that has developed the intervention content in collaboration with key stakeholders such as patients or community members.</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr"/>
-      <c r="R111" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
       <c r="S111" t="inlineStr"/>
       <c r="T111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>BCIO:010082</t>
+          <t>BCIO:010133</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
@@ -4626,38 +4707,34 @@
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>armed forces occupation</t>
-        </is>
-      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>source role related to intervention</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr"/>
       <c r="N112" t="inlineStr">
         <is>
-          <t>An occupational role that includes all jobs held by members of the armed forces.</t>
+          <t>A BCI source whose occupational or voluntary role is focused on delivery of the behaviour change intervention.</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr"/>
-      <c r="R112" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
       <c r="S112" t="inlineStr"/>
-      <c r="T112" t="inlineStr">
-        <is>
-          <t>Admiral, Air commodore, Air marshal, Airman, Brigadier (army), Bombardier, Captain (air force), Captain (army), Captain (navy), Colonel (army), Corporal,  Field marshal, Flight lieutenant (air force), Flying officer (military), General (army), Gunner, Group captain, (air force), Lieutenant (army), Major (army), Midshipman, Naval officer (military) , Navy commander, Officer cadet (armed forces), Paratrooper, Rifleman, Sergeant (army), Second lieutenant (army), Seaman, Squadron leader, Sublieutenant (navy), Wing commander</t>
-        </is>
-      </c>
+      <c r="T112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>BCIO:010078</t>
+          <t>BCIO:006081</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -4665,39 +4742,35 @@
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>personal role</t>
+        </is>
+      </c>
       <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>craft and related trades worker</t>
-        </is>
-      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr">
         <is>
-          <t>An occupational role that applies specific technical and practical knowledge and skills to construct and maintain buildings, machinery, equipment or tools, carries out printing work, and produces or processes foodstuffs, textiles and wooden, metal and other articles, including handicraft goods.</t>
+          <t>A role that inheres in a human being by virtue of their social and institutional circumstances.</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr"/>
       <c r="R113" t="inlineStr">
         <is>
-          <t>Source</t>
+          <t>A role can be assigned without being realised. A person realises a role by doing something.</t>
         </is>
       </c>
       <c r="S113" t="inlineStr"/>
-      <c r="T113" t="inlineStr">
-        <is>
-          <t>Building Trade Worker, Metal Workers, Machinery Worker, Handicraft Worker, Printing Worker, Electrical Equipment Installers and Repairer, Electronics and Telecommunications Installer and Repairer, Food Processing Worker, Woodworker, Tobacco Product Maker</t>
-        </is>
-      </c>
+      <c r="T113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>BCIO:010068</t>
+          <t>BCIO:010084</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
@@ -4706,34 +4779,34 @@
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>services and sales worker</t>
-        </is>
-      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>student or trainee role</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr">
         <is>
-          <t>An occupational role that provides personal or protective services related to travel, house-keeping, catering, personal care, protection against fire and unlawful acts, or sells goods in retail or markets.</t>
+          <t>A personal role which inheres in a person and is realised by being enrolled in an educational institution or a formal programme of professional training.</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr"/>
-      <c r="R114" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
       <c r="S114" t="inlineStr"/>
       <c r="T114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>BCIO:010070</t>
+          <t>BCIO:010087</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
@@ -4743,37 +4816,33 @@
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>sales worker</t>
-        </is>
-      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>trainee role</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr">
         <is>
-          <t>A services and sales worker that demonstrates goods in wholesale or retail shops, at stalls and markets, door to door, via telephone or customer contact centres. They may record and accept payment for goods and services purchased, and may operate small retail outlets.</t>
+          <t>A student or trainee role that is currently learning the curriculum material of vocational programme, normally in preparation for employment in a trade, job or profession.</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr"/>
-      <c r="R115" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
       <c r="S115" t="inlineStr"/>
-      <c r="T115" t="inlineStr">
-        <is>
-          <t>Street Salesperson, Market Salesperson, Shop Salesperson, Cashier, Ticket Clerk, Model, Sales Demonstrator, Door-to-door Salesperson, Contact Centre Salesperson, Service Station Attendant, Food Service Counter Attendant</t>
-        </is>
-      </c>
+      <c r="T115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>BCIO:010071</t>
+          <t>BCIO:010086</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -4783,37 +4852,33 @@
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>personal care worker</t>
-        </is>
-      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>school student role</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr">
         <is>
-          <t>A services and sales worker that provides care, supervision and assistance for children, patients and elderly, convalescent or disabled persons in institutional and residential settings.</t>
+          <t>A student or trainee role realised by currently learning at a primary or secondary education level in an institutional, organised setting.</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr"/>
-      <c r="R116" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
       <c r="S116" t="inlineStr"/>
-      <c r="T116" t="inlineStr">
-        <is>
-          <t>Personal carer</t>
-        </is>
-      </c>
+      <c r="T116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>BCIO:010073</t>
+          <t>BCIO:010088</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -4823,37 +4888,37 @@
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>higher education student role</t>
+        </is>
+      </c>
       <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>teachers’ aide</t>
-        </is>
-      </c>
+      <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr">
         <is>
-          <t>A personal care worker that performs non-teaching duties to assist teaching staff, and provides care and supervision for children in schools and pre-schools.</t>
-        </is>
-      </c>
-      <c r="Q117" t="inlineStr"/>
-      <c r="R117" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A student or trainee role realised by currently learning on an advanced educational programme in a university, college or professional school.</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>completing a university bachelor's or master's course of study, medical school or other professional school.</t>
         </is>
       </c>
       <c r="S117" t="inlineStr"/>
-      <c r="T117" t="inlineStr">
-        <is>
-          <t>Pre-school assistant, Teacher’s assistant</t>
-        </is>
-      </c>
+      <c r="T117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>BCIO:010072</t>
+          <t>BCIO:010092</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
@@ -4864,36 +4929,36 @@
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>child care worker</t>
-        </is>
-      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>doctoral student role</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr">
         <is>
-          <t>A personal care worker that provides care and supervision for children in non-domestic settings.</t>
-        </is>
-      </c>
-      <c r="Q118" t="inlineStr"/>
-      <c r="R118" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A higher education student  role realised by currently studying for a doctoral degree.</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>PhD student</t>
         </is>
       </c>
       <c r="S118" t="inlineStr"/>
-      <c r="T118" t="inlineStr">
-        <is>
-          <t>Babysitter, Child care worker, Creche ayah, Family day care worker, Nanny, Out of school hours care worker</t>
-        </is>
-      </c>
+      <c r="T118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>BCIO:010074</t>
+          <t>BCIO:010091</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
@@ -4904,36 +4969,36 @@
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>health care assistant</t>
-        </is>
-      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>masters student role</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr">
         <is>
-          <t>A personal care worker that provides direct personal care and assistance with activities of daily living to patients and residents in a variety of health care settings, working  in implementation of established care plans and practices, and under the direct supervision of medical, nursing or other health professionals or associate professionals.</t>
-        </is>
-      </c>
-      <c r="Q119" t="inlineStr"/>
-      <c r="R119" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A higher education student  role realised by currently studying for a masters degree.</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>MSc student, Masters student</t>
         </is>
       </c>
       <c r="S119" t="inlineStr"/>
-      <c r="T119" t="inlineStr">
-        <is>
-          <t>Nursing aide (clinic or hospital), Patient care assistant, Psychiatric aid</t>
-        </is>
-      </c>
+      <c r="T119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>BCIO:010075</t>
+          <t>BCIO:010089</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
@@ -4944,36 +5009,36 @@
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>home-based personal care worker</t>
-        </is>
-      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>undergraduate student role</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr"/>
       <c r="N120" t="inlineStr">
         <is>
-          <t>A personal care worker that provide routine personal care and assistance with activities of daily living to persons who are in need of such care due to effects of ageing, illness, injury, or other physical or mental conditions, in private homes and other independent residential settings.</t>
-        </is>
-      </c>
-      <c r="Q120" t="inlineStr"/>
-      <c r="R120" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A higher education student role realised by currently studying for an undergraduate degree.</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>undergraduate student</t>
         </is>
       </c>
       <c r="S120" t="inlineStr"/>
-      <c r="T120" t="inlineStr">
-        <is>
-          <t>Home birth assistant, Home care aide, Nursing aide (home), Personal care provider</t>
-        </is>
-      </c>
+      <c r="T120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>BCIO:010076</t>
+          <t>BCIO:010090</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
@@ -4986,7 +5051,7 @@
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr">
         <is>
-          <t>protective services worker</t>
+          <t>graduate student role</t>
         </is>
       </c>
       <c r="K121" t="inlineStr"/>
@@ -4994,26 +5059,26 @@
       <c r="M121" t="inlineStr"/>
       <c r="N121" t="inlineStr">
         <is>
-          <t>A services and sales worker that protects individuals and property against fire and other hazards, maintain law and order and enforce laws and regulations.</t>
-        </is>
-      </c>
-      <c r="Q121" t="inlineStr"/>
-      <c r="R121" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A higher education student role realised by currently studying for a more advanced degree after completing an undergraduate degree.</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>graduate student</t>
         </is>
       </c>
       <c r="S121" t="inlineStr"/>
-      <c r="T121" t="inlineStr">
-        <is>
-          <t>Firefighter, Police officer, Prison guard, Security guard, Offender manager</t>
-        </is>
-      </c>
+      <c r="T121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>BCIO:010069</t>
+          <t>BCIO:010085</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
@@ -5023,37 +5088,33 @@
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>personal services worker</t>
-        </is>
-      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>informal education student role</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr"/>
       <c r="N122" t="inlineStr">
         <is>
-          <t>A services and sales worker that provides personal services related to travel, housekeeping, catering and hospitality, hairdressing and beauty treatment, animal care grooming and training, companionship and other services of a personal nature.</t>
+          <t>A student or trainee role that is currently learning in a non-institutional setting.</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
       <c r="Q122" t="inlineStr"/>
-      <c r="R122" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
       <c r="S122" t="inlineStr"/>
-      <c r="T122" t="inlineStr">
-        <is>
-          <t>Travel Attendant, Conductor, Guide, Cook, Waiter, Bartender, Hairdresser, Beautician, Housekeeping Supervisor, Astrologer, Fortune-teller, Valet, Undertaker, Embalmer, Pet Groomer, Animal Care Worker</t>
-        </is>
-      </c>
+      <c r="T122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>BCIO:010005</t>
+          <t>BCIO:051024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
@@ -5062,78 +5123,52 @@
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr"/>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>manager</t>
-        </is>
-      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>certified professional role</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr"/>
       <c r="N123" t="inlineStr">
         <is>
-          <t>An occupational role of source that manages, plans and coordinates the overall activities of enterprises, governments and other organisations.</t>
+          <t>A personal role that inheres in a human being by virtue of formal recognition of their competence by a professional or regulatory body.</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr"/>
-      <c r="R123" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
       <c r="S123" t="inlineStr"/>
-      <c r="T123" t="inlineStr">
-        <is>
-          <t>Chief Executive Officers; Administrative Managers;  Commercial Managers</t>
-        </is>
-      </c>
+      <c r="T123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>BCIO:010077</t>
+          <t>BFO:0000016</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr"/>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>disposition</t>
+        </is>
+      </c>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>skilled agricultural, forestry and fishery worker</t>
-        </is>
-      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr"/>
-      <c r="N124" t="inlineStr">
-        <is>
-          <t>An occupational role that grows and harvests plants or animals to provide food, shelter and income for themselves and their households.</t>
-        </is>
-      </c>
-      <c r="Q124" t="inlineStr"/>
-      <c r="R124" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S124" t="inlineStr"/>
-      <c r="T124" t="inlineStr">
-        <is>
-          <t>Market gardener, Crop grower, Animal Producer, Mixed Crop and Animal Producer, Forestry worker, Fishery worker, Hunter. Subsistence Crop Farmer, Subsistence Livestock Farmer</t>
-        </is>
-      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>BCIO:010067</t>
+          <t>BCIO:010120</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
@@ -5141,39 +5176,35 @@
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>expertise of person source</t>
+        </is>
+      </c>
       <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>clerical support worker</t>
-        </is>
-      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr"/>
       <c r="M125" t="inlineStr"/>
       <c r="N125" t="inlineStr">
         <is>
-          <t>An occupational role that records, organizes, stores, computes and retrieves information, and performs a number of clerical duties in connection with money-handling operations, travel arrangements, requests for information, and appointments.</t>
+          <t>A disposition that is an expert skill or knowledge held by the source delivering the behaviour change intervention.</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr"/>
-      <c r="R125" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
       <c r="S125" t="inlineStr"/>
-      <c r="T125" t="inlineStr">
-        <is>
-          <t>General and Keyboard Clerk, customers Services Clerk, Numerical and Material Recording Clerk</t>
-        </is>
-      </c>
+      <c r="T125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>BCIO:010094</t>
+          <t>BCIO:010125</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -5184,7 +5215,7 @@
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr">
         <is>
-          <t>relatedness between person source and the target population</t>
+          <t>acquired expertise</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -5194,22 +5225,22 @@
       <c r="M126" t="inlineStr"/>
       <c r="N126" t="inlineStr">
         <is>
-          <t>A personal role of source that is realised in some relationship to the characteristics of the intervention participants.</t>
+          <t>An expertise of person source that is additional knowledge or skills supplied to the source to allow them to deliver the intervention, including educational level and qualifications.</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr"/>
-      <c r="R126" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
       <c r="S126" t="inlineStr"/>
       <c r="T126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>BCIO:010102</t>
+          <t>BCIO:010122</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
@@ -5218,25 +5249,29 @@
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr"/>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>colleague</t>
-        </is>
-      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>pre-existing expertise</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr"/>
       <c r="M127" t="inlineStr"/>
       <c r="N127" t="inlineStr">
         <is>
-          <t>A relatedness between person source and the target population that is a person with whom the participant works in a profession or business.</t>
-        </is>
-      </c>
-      <c r="Q127" t="inlineStr"/>
-      <c r="R127" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>An expertise of person source that is already possessed by the source which allows them to deliver the intervention, including educational level and qualifications.</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree, certification, accredited, qualified</t>
         </is>
       </c>
       <c r="S127" t="inlineStr"/>
@@ -5245,79 +5280,63 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>BCIO:010105</t>
+          <t>MF:0000030</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>representation</t>
+        </is>
+      </c>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>embedded in participants’ community</t>
-        </is>
-      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr"/>
       <c r="N128" t="inlineStr">
         <is>
-          <t>A relatedness between person source and the target population that is a source who is known and working to deliver intervention in own community.</t>
-        </is>
-      </c>
-      <c r="Q128" t="inlineStr"/>
-      <c r="R128" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S128" t="inlineStr"/>
-      <c r="T128" t="inlineStr"/>
+          <t>A dependent continuant which is about a portion of reality.</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>BCIO:010104</t>
+          <t>MF:0000031</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr"/>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>cognitive representation</t>
+        </is>
+      </c>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>peer</t>
-        </is>
-      </c>
+      <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr"/>
       <c r="N129" t="inlineStr">
         <is>
-          <t>A relatedness between person source and the target population that is descried as matched to intervention recipients on the basis of ‘peerness’ – age, social status, gender, shared experience, shared health status etc.</t>
-        </is>
-      </c>
-      <c r="Q129" t="inlineStr"/>
-      <c r="R129" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S129" t="inlineStr"/>
-      <c r="T129" t="inlineStr"/>
+          <t>A representation which specifically depends on an anatomical structure in the cognitive system of an organism.</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>BCIO:010101</t>
+          <t>ADDICTO:0000381</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
@@ -5325,35 +5344,27 @@
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
       <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>friend</t>
-        </is>
-      </c>
+      <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr"/>
       <c r="M130" t="inlineStr"/>
       <c r="N130" t="inlineStr">
         <is>
-          <t>A relatedness between person source and the target population that is a person whom the participant knows, likes and trusts, typically exclusive of sexual or family relations.</t>
-        </is>
-      </c>
-      <c r="Q130" t="inlineStr"/>
-      <c r="R130" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S130" t="inlineStr"/>
-      <c r="T130" t="inlineStr"/>
+          <t>A cognitive representation of themselves by a person or a group about themselves.</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>BCIO:010103</t>
+          <t>ADDICTO:0000399</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
@@ -5362,34 +5373,26 @@
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr"/>
-      <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>employer</t>
-        </is>
-      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>self-identity</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr"/>
       <c r="M131" t="inlineStr"/>
       <c r="N131" t="inlineStr">
         <is>
-          <t>A relatedness between person source and the target population that is a person which hires the services of the participant.</t>
-        </is>
-      </c>
-      <c r="Q131" t="inlineStr"/>
-      <c r="R131" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S131" t="inlineStr"/>
-      <c r="T131" t="inlineStr"/>
+          <t>An identity that a person has about themselves.</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>BCIO:010100</t>
+          <t>BCIO:015098</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
@@ -5401,7 +5404,7 @@
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
-          <t>carer</t>
+          <t>gender identity</t>
         </is>
       </c>
       <c r="J132" t="inlineStr"/>
@@ -5410,49 +5413,62 @@
       <c r="M132" t="inlineStr"/>
       <c r="N132" t="inlineStr">
         <is>
-          <t>A relatedness between person source and the target population that is an individual who cares, unpaid, for a friend or family member who, due to illness or disability, requires support in their daily life activities.</t>
+          <t>A self-identity as having a particular gender, which may or may not correspond with sex assigned at birth.</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>Population</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr"/>
-      <c r="R132" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
       <c r="S132" t="inlineStr"/>
-      <c r="T132" t="inlineStr">
-        <is>
-          <t>carer</t>
-        </is>
-      </c>
+      <c r="T132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>BFO:0000016</t>
+          <t>BCIO:010111</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>disposition</t>
-        </is>
-      </c>
+      <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>female gender</t>
+        </is>
+      </c>
       <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>A gender identity as being female.</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>female, woman</t>
+        </is>
+      </c>
+      <c r="S133" t="inlineStr"/>
+      <c r="T133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>BCIO:010120</t>
+          <t>BCIO:010112</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
@@ -5460,26 +5476,30 @@
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>expertise of person source</t>
-        </is>
-      </c>
+      <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>male gender</t>
+        </is>
+      </c>
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr"/>
       <c r="M134" t="inlineStr"/>
       <c r="N134" t="inlineStr">
         <is>
-          <t>A disposition that is an expert skill or knowledge held by the source delivering the behaviour change intervention.</t>
-        </is>
-      </c>
-      <c r="Q134" t="inlineStr"/>
-      <c r="R134" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A gender identity as being male.</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>male, man</t>
         </is>
       </c>
       <c r="S134" t="inlineStr"/>
@@ -5488,20 +5508,20 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>BCIO:010122</t>
+          <t>BCIO:010108</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr"/>
-      <c r="E135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>socio demographic attribute of person source</t>
+        </is>
+      </c>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr"/>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>pre-existing expertise</t>
-        </is>
-      </c>
+      <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
@@ -5509,39 +5529,35 @@
       <c r="M135" t="inlineStr"/>
       <c r="N135" t="inlineStr">
         <is>
-          <t>An expertise of person source that is already possessed by the source which allows them to deliver the intervention, including educational level and qualifications.</t>
+          <t>A social or demographic characteristic of a human being who is the bearer of a person source role.</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr"/>
-      <c r="R135" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
       <c r="S135" t="inlineStr"/>
-      <c r="T135" t="inlineStr">
-        <is>
-          <t>Bachelor’s degree, certification, accredited, qualified</t>
-        </is>
-      </c>
+      <c r="T135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>BCIO:010125</t>
+          <t>BCIO:010115</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr"/>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>religious group membership of person source</t>
+        </is>
+      </c>
       <c r="G136" t="inlineStr"/>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>acquired expertise</t>
-        </is>
-      </c>
+      <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
@@ -5549,13 +5565,17 @@
       <c r="M136" t="inlineStr"/>
       <c r="N136" t="inlineStr">
         <is>
-          <t>An expertise of person source that is additional knowledge or skills supplied to the source to allow them to deliver the intervention, including educational level and qualifications.</t>
-        </is>
-      </c>
-      <c r="Q136" t="inlineStr"/>
-      <c r="R136" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A socio-demographic attribute of person source that is a religious group to which an individual identifies as belonging, where a religious group is a group of people characterised by the practice of a common religion.</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>Muslim, Christian, Hindu, Sikh, Buddhist, Judaism</t>
         </is>
       </c>
       <c r="S136" t="inlineStr"/>
@@ -5564,18 +5584,18 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>MF:0000030</t>
+          <t>BCIO:010114</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr"/>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>representation</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr"/>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>ethnic group membership of person source</t>
+        </is>
+      </c>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr"/>
@@ -5585,14 +5605,26 @@
       <c r="M137" t="inlineStr"/>
       <c r="N137" t="inlineStr">
         <is>
-          <t>A dependent continuant which is about a portion of reality.</t>
-        </is>
-      </c>
+          <t>A socio-demographic attribute of person source that is the ethnic group to which an individual identifies as belonging, where an ethic group is a population whose members have a common heritage that is real or presumed such as common culture, language, religion, behaviour or biological trait.</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>black, white, Indian, Chinese, Somalian</t>
+        </is>
+      </c>
+      <c r="S137" t="inlineStr"/>
+      <c r="T137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>MF:0000031</t>
+          <t>BCIO:010116</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
@@ -5601,7 +5633,7 @@
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>cognitive representation</t>
+          <t>language proficiency of person source</t>
         </is>
       </c>
       <c r="G138" t="inlineStr"/>
@@ -5613,26 +5645,38 @@
       <c r="M138" t="inlineStr"/>
       <c r="N138" t="inlineStr">
         <is>
-          <t>A representation which specifically depends on an anatomical structure in the cognitive system of an organism.</t>
-        </is>
-      </c>
+          <t>A socio-demographic attribute of person source that is an individual’s ability to speak or perform in the intervention language.</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>fluent, native</t>
+        </is>
+      </c>
+      <c r="S138" t="inlineStr"/>
+      <c r="T138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ADDICTO:0000381</t>
+          <t>BCIO:010117</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>identity</t>
-        </is>
-      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>health status of person source</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr"/>
@@ -5641,27 +5685,39 @@
       <c r="M139" t="inlineStr"/>
       <c r="N139" t="inlineStr">
         <is>
-          <t>A cognitive representation of themselves by a person or a group about themselves.</t>
-        </is>
-      </c>
+          <t>A socio-demographic attribute of person source that represents their mental or physical condition.</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>diabetes, cancer, depression, obesity, overweight</t>
+        </is>
+      </c>
+      <c r="S139" t="inlineStr"/>
+      <c r="T139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ADDICTO:0000399</t>
+          <t>BCIO:010119</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr"/>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>psychological influence on intervention delivery of person source</t>
+        </is>
+      </c>
       <c r="G140" t="inlineStr"/>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>self-identity</t>
-        </is>
-      </c>
+      <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
@@ -5669,142 +5725,150 @@
       <c r="M140" t="inlineStr"/>
       <c r="N140" t="inlineStr">
         <is>
-          <t>An identity that a person has about themselves.</t>
-        </is>
-      </c>
+          <t>A socio-demographic attribute of person source that is their existing psychological attributes related to or potentially affecting the target behaviour.</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr"/>
+      <c r="S140" t="inlineStr"/>
+      <c r="T140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>BCIO:015098</t>
+          <t>BCIO:010109</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr"/>
-      <c r="F141" t="inlineStr"/>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>age of person source</t>
+        </is>
+      </c>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr"/>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>gender identity</t>
-        </is>
-      </c>
+      <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr"/>
       <c r="M141" t="inlineStr"/>
       <c r="N141" t="inlineStr">
         <is>
-          <t>A self-identity as having a particular gender, which may or may not correspond with sex assigned at birth.</t>
+          <t>A socio-demographic attribute of person source that is a time quality inhering in a bearer by virtue of how long the bearer has existed.</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
       <c r="Q141" t="inlineStr"/>
-      <c r="R141" t="inlineStr">
-        <is>
-          <t>Population</t>
-        </is>
-      </c>
       <c r="S141" t="inlineStr"/>
       <c r="T141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>BCIO:010111</t>
+          <t>BCIO:010118</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr"/>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>target behaviour of person source</t>
+        </is>
+      </c>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>female gender</t>
-        </is>
-      </c>
+      <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr"/>
       <c r="M142" t="inlineStr"/>
       <c r="N142" t="inlineStr">
         <is>
-          <t>A gender identity as being female.</t>
-        </is>
-      </c>
-      <c r="Q142" t="inlineStr"/>
-      <c r="R142" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A socio-demographic attribute of person source that is their amount or experience of the intervention’s target behaviour.</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>source is highly physically active</t>
         </is>
       </c>
       <c r="S142" t="inlineStr"/>
-      <c r="T142" t="inlineStr">
-        <is>
-          <t>female, woman</t>
-        </is>
-      </c>
+      <c r="T142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>BCIO:010112</t>
+          <t>BCIO:010110</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr"/>
-      <c r="F143" t="inlineStr"/>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>gender of person source</t>
+        </is>
+      </c>
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>male gender</t>
-        </is>
-      </c>
+      <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr"/>
       <c r="N143" t="inlineStr">
         <is>
-          <t>A gender identity as being male.</t>
-        </is>
-      </c>
-      <c r="Q143" t="inlineStr"/>
-      <c r="R143" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A socio-demographic attribute of person source that is an individual's perception of having a particular gender, which may or may not correspond with their birth sex.</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>gender</t>
         </is>
       </c>
       <c r="S143" t="inlineStr"/>
-      <c r="T143" t="inlineStr">
-        <is>
-          <t>male, man</t>
-        </is>
-      </c>
+      <c r="T143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>BCIO:010123</t>
+          <t>BCIO:010113</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr"/>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>expertise discipline</t>
-        </is>
-      </c>
+      <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>other gender</t>
+        </is>
+      </c>
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr"/>
@@ -5813,42 +5877,37 @@
       <c r="M144" t="inlineStr"/>
       <c r="N144" t="inlineStr">
         <is>
-          <t>An attribute that is a field of knowledge or practice.</t>
+          <t>A gender of person source that reports not belonging to the cultural gender role distinctions of either male or female.</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>The division of expertise into different disciplines or fields is complex and depends on historical, social and structural factors.</t>
-        </is>
-      </c>
-      <c r="Q144" t="inlineStr"/>
-      <c r="R144" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>non-binary, transexual</t>
         </is>
       </c>
       <c r="S144" t="inlineStr"/>
-      <c r="T144" t="inlineStr">
-        <is>
-          <t>psychology, yoga, cognitive behavioural therapy, hypnotism</t>
-        </is>
-      </c>
+      <c r="T144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>BCIO:010124</t>
+          <t>BFO:0000004</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr"/>
-      <c r="D145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>independent continuant</t>
+        </is>
+      </c>
       <c r="E145" t="inlineStr"/>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>discipline of pre-existing expertise</t>
-        </is>
-      </c>
+      <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr"/>
@@ -5858,37 +5917,25 @@
       <c r="M145" t="inlineStr"/>
       <c r="N145" t="inlineStr">
         <is>
-          <t>The expertise discipline in which the person source has acquired their pre-existing knowledge and skills.</t>
-        </is>
-      </c>
-      <c r="Q145" t="inlineStr"/>
-      <c r="R145" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S145" t="inlineStr"/>
-      <c r="T145" t="inlineStr">
-        <is>
-          <t>psychology, yoga, cognitive behavioural therapy, hypnotism</t>
+          <t>A continuant that is a bearer of quality and realizable entity entities, in which other entities inhere and which itself cannot inhere in anything.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>BCIO:010093</t>
+          <t>BFO:0000040</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr"/>
-      <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>discipline of current programme of study or training</t>
-        </is>
-      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>material entity</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr"/>
@@ -5898,37 +5945,25 @@
       <c r="M146" t="inlineStr"/>
       <c r="N146" t="inlineStr">
         <is>
-          <t>An expertise discipline of the programme of study currently undertaken by the bearer of a student or trainee role.</t>
-        </is>
-      </c>
-      <c r="Q146" t="inlineStr"/>
-      <c r="R146" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S146" t="inlineStr"/>
-      <c r="T146" t="inlineStr">
-        <is>
-          <t>psychology, medicine, hairdressing</t>
+          <t>An independent continuant that is spatially extended whose identity is independent of that of other entities and can be maintained through time.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>BCIO:010108</t>
+          <t>BCIO:010139</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr"/>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>socio demographic attribute of person source</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr"/>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>organisation source</t>
+        </is>
+      </c>
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr"/>
@@ -5938,22 +5973,22 @@
       <c r="M147" t="inlineStr"/>
       <c r="N147" t="inlineStr">
         <is>
-          <t>A social or demographic characteristic of a human being who is the bearer of a person source role.</t>
+          <t>An organisation that is the bearer of a behaviour change intervention source role, such as voluntary, public or commercial organisations delivering a behaviour change intervention.</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
       <c r="Q147" t="inlineStr"/>
-      <c r="R147" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
       <c r="S147" t="inlineStr"/>
       <c r="T147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>BCIO:010109</t>
+          <t>OBI:0000245</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
@@ -5962,7 +5997,7 @@
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>age of person source</t>
+          <t>organization</t>
         </is>
       </c>
       <c r="G148" t="inlineStr"/>
@@ -5974,22 +6009,22 @@
       <c r="M148" t="inlineStr"/>
       <c r="N148" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is a time quality inhering in a bearer by virtue of how long the bearer has existed.</t>
+          <t>An entity that can bear roles, has members, and has a set of organization rules. Members of organizations are either organizations themselves or individual people. Members can bear specific organization member roles that are determined in the organization rules. The organization rules also determine how decisions are made on behalf of the organization by the organization members.</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
       <c r="Q148" t="inlineStr"/>
-      <c r="R148" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
       <c r="S148" t="inlineStr"/>
       <c r="T148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>BCIO:010110</t>
+          <t>OGMS:0000087</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
@@ -5998,7 +6033,7 @@
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>gender of person source</t>
+          <t>extended organism</t>
         </is>
       </c>
       <c r="G149" t="inlineStr"/>
@@ -6010,26 +6045,14 @@
       <c r="M149" t="inlineStr"/>
       <c r="N149" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is an individual's perception of having a particular gender, which may or may not correspond with their birth sex.</t>
-        </is>
-      </c>
-      <c r="Q149" t="inlineStr"/>
-      <c r="R149" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S149" t="inlineStr"/>
-      <c r="T149" t="inlineStr">
-        <is>
-          <t>gender</t>
+          <t>An object aggregate consisting of an organism and all material entities located within the organism, overlapping the organism, or occupying sites formed in part by the organism.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>BCIO:010113</t>
+          <t>MF:0000016</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
@@ -6039,7 +6062,7 @@
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr">
         <is>
-          <t>other gender</t>
+          <t>person</t>
         </is>
       </c>
       <c r="H150" t="inlineStr"/>
@@ -6050,39 +6073,35 @@
       <c r="M150" t="inlineStr"/>
       <c r="N150" t="inlineStr">
         <is>
-          <t>A gender of person source that reports not belonging to the cultural gender role distinctions of either male or female.</t>
+          <t>An extended organism that is a member of the species Homo sapiens.</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
       <c r="Q150" t="inlineStr"/>
-      <c r="R150" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
       <c r="S150" t="inlineStr"/>
-      <c r="T150" t="inlineStr">
-        <is>
-          <t>non-binary, transexual</t>
-        </is>
-      </c>
+      <c r="T150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>BCIO:010116</t>
+          <t>BCIO:050842</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr"/>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>language proficiency of person source</t>
-        </is>
-      </c>
+      <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr"/>
-      <c r="H151" t="inlineStr"/>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>role model for a person</t>
+        </is>
+      </c>
       <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr"/>
@@ -6090,39 +6109,40 @@
       <c r="M151" t="inlineStr"/>
       <c r="N151" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is an individual’s ability to speak or perform in the intervention language.</t>
+          <t>A &lt;person&gt; that influences a recipient by being perceived to be similar or admired.</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
       <c r="Q151" t="inlineStr"/>
       <c r="R151" t="inlineStr">
         <is>
-          <t>Source</t>
+          <t>This class lies at the intersection between a person and their environment and is defined from the perspective of the person.</t>
         </is>
       </c>
       <c r="S151" t="inlineStr"/>
-      <c r="T151" t="inlineStr">
-        <is>
-          <t>fluent, native</t>
-        </is>
-      </c>
+      <c r="T151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>BCIO:010119</t>
+          <t>BCIO:010095</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>psychological influence on intervention delivery of person source</t>
-        </is>
-      </c>
+      <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr"/>
-      <c r="H152" t="inlineStr"/>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>family member</t>
+        </is>
+      </c>
       <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr"/>
@@ -6130,195 +6150,195 @@
       <c r="M152" t="inlineStr"/>
       <c r="N152" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is their existing psychological attributes related to or potentially affecting the target behaviour.</t>
+          <t>A person who is a member of a group of persons united by blood, or by marriage or other legal arrangement, or by self-identity as belonging to the same family.</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
       <c r="Q152" t="inlineStr"/>
-      <c r="R152" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
       <c r="S152" t="inlineStr"/>
       <c r="T152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>BCIO:010117</t>
+          <t>BCIO:010098</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr"/>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>health status of person source</t>
-        </is>
-      </c>
+      <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr"/>
-      <c r="I153" t="inlineStr"/>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>sibling relationship</t>
+        </is>
+      </c>
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr"/>
       <c r="M153" t="inlineStr"/>
       <c r="N153" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that represents their mental or physical condition.</t>
-        </is>
-      </c>
-      <c r="Q153" t="inlineStr"/>
-      <c r="R153" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A family member that is a family relationship between two persons with at least one shared parent.</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>brother, sister, step-brother, step-sister</t>
         </is>
       </c>
       <c r="S153" t="inlineStr"/>
-      <c r="T153" t="inlineStr">
-        <is>
-          <t>diabetes, cancer, depression, obesity, overweight</t>
-        </is>
-      </c>
+      <c r="T153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>BCIO:010118</t>
+          <t>BCIO:010099</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr"/>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>target behaviour of person source</t>
-        </is>
-      </c>
+      <c r="F154" t="inlineStr"/>
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr"/>
-      <c r="I154" t="inlineStr"/>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>child relationship</t>
+        </is>
+      </c>
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr"/>
       <c r="M154" t="inlineStr"/>
       <c r="N154" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is their amount or experience of the intervention’s target behaviour.</t>
-        </is>
-      </c>
-      <c r="Q154" t="inlineStr"/>
-      <c r="R154" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A family member that is an offspring relationship from a person to their parent.</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>daughter, son, step-daughter, step-son</t>
         </is>
       </c>
       <c r="S154" t="inlineStr"/>
-      <c r="T154" t="inlineStr">
-        <is>
-          <t>source is highly physically active</t>
-        </is>
-      </c>
+      <c r="T154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>BCIO:010115</t>
+          <t>BCIO:010096</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr"/>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>religious group membership of person source</t>
-        </is>
-      </c>
+      <c r="F155" t="inlineStr"/>
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr"/>
-      <c r="I155" t="inlineStr"/>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>parent or guardian</t>
+        </is>
+      </c>
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr"/>
       <c r="M155" t="inlineStr"/>
       <c r="N155" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is a religious group to which an individual identifies as belonging, where a religious group is a group of people characterised by the practice of a common religion.</t>
-        </is>
-      </c>
-      <c r="Q155" t="inlineStr"/>
-      <c r="R155" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A family member that is a mother, father or legal carer of a child.</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>mother, father, step-mother, step-father, guardian</t>
         </is>
       </c>
       <c r="S155" t="inlineStr"/>
-      <c r="T155" t="inlineStr">
-        <is>
-          <t>Muslim, Christian, Hindu, Sikh, Buddhist, Judaism</t>
-        </is>
-      </c>
+      <c r="T155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>BCIO:010114</t>
+          <t>BCIO:010097</t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr"/>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>ethnic group membership of person source</t>
-        </is>
-      </c>
+      <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr"/>
-      <c r="I156" t="inlineStr"/>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>spouse or partner</t>
+        </is>
+      </c>
       <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr"/>
       <c r="M156" t="inlineStr"/>
       <c r="N156" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is the ethnic group to which an individual identifies as belonging, where an ethic group is a population whose members have a common heritage that is real or presumed such as common culture, language, religion, behaviour or biological trait.</t>
-        </is>
-      </c>
-      <c r="Q156" t="inlineStr"/>
-      <c r="R156" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A family member that is an individual who is married or in a committed relationship with another individual.</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>boyfriend, girlfriend, partner, fiance, wife, husband</t>
         </is>
       </c>
       <c r="S156" t="inlineStr"/>
-      <c r="T156" t="inlineStr">
-        <is>
-          <t>black, white, Indian, Chinese, Somalian</t>
-        </is>
-      </c>
+      <c r="T156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>BFO:0000003</t>
+          <t>BCIO:010002</t>
         </is>
       </c>
       <c r="B157" t="inlineStr"/>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>occurrent</t>
-        </is>
-      </c>
+      <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="inlineStr"/>
-      <c r="H157" t="inlineStr"/>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>person source</t>
+        </is>
+      </c>
       <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
@@ -6326,21 +6346,29 @@
       <c r="M157" t="inlineStr"/>
       <c r="N157" t="inlineStr">
         <is>
-          <t>An entity that has temporal parts and that happens, unfolds or develops through time.</t>
-        </is>
-      </c>
+          <t>A person who is the bearer of a behaviour change intervention source role.</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr"/>
+      <c r="S157" t="inlineStr"/>
+      <c r="T157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>BFO:0000015</t>
+          <t>BFO:0000031</t>
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
-          <t>process</t>
+          <t>generically dependent continuant</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -6354,14 +6382,14 @@
       <c r="M158" t="inlineStr"/>
       <c r="N158" t="inlineStr">
         <is>
-          <t>An occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t.</t>
+          <t>b is a generically dependent continuant = Def. b is a continuant that g-depends_on one or more other entities. (axiom label in BFO2 Reference: [074-001])</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>BCIO:010130</t>
+          <t>IAO:0000030</t>
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
@@ -6369,7 +6397,7 @@
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
-          <t>payment of person source</t>
+          <t>information content entity</t>
         </is>
       </c>
       <c r="F159" t="inlineStr"/>
@@ -6382,22 +6410,14 @@
       <c r="M159" t="inlineStr"/>
       <c r="N159" t="inlineStr">
         <is>
-          <t>A process in which a person source is paid or compensated for delivering the intervention.</t>
-        </is>
-      </c>
-      <c r="Q159" t="inlineStr"/>
-      <c r="R159" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S159" t="inlineStr"/>
-      <c r="T159" t="inlineStr"/>
+          <t>A generically dependent continuant that is about some thing.</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>BCIO:010131</t>
+          <t>IAO:0000027</t>
         </is>
       </c>
       <c r="B160" t="inlineStr"/>
@@ -6406,7 +6426,7 @@
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
-          <t>monetary payment</t>
+          <t>data item</t>
         </is>
       </c>
       <c r="G160" t="inlineStr"/>
@@ -6418,38 +6438,26 @@
       <c r="M160" t="inlineStr"/>
       <c r="N160" t="inlineStr">
         <is>
-          <t>A payment of person source that is money, vouchers or valued objects given to the source for delivering the intervention.</t>
-        </is>
-      </c>
-      <c r="Q160" t="inlineStr"/>
-      <c r="R160" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S160" t="inlineStr"/>
-      <c r="T160" t="inlineStr">
-        <is>
-          <t>paid in cash, vouchers</t>
+          <t>An information content entity that is intended to be one or more truthful statement(s) about something (modulo, e.g., measurement precision or other systematic errors) and is constructed/acquired by a method which reliably tends to produce (approximately) truthful statements.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>BCIO:010132</t>
+          <t>BCIO:010126</t>
         </is>
       </c>
       <c r="B161" t="inlineStr"/>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr"/>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>non-monetary payment</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr"/>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>amount of experience</t>
+        </is>
+      </c>
       <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr"/>
@@ -6458,38 +6466,38 @@
       <c r="M161" t="inlineStr"/>
       <c r="N161" t="inlineStr">
         <is>
-          <t>A payment of person source that is non-monetary compensation given to the source for delivering the intervention.</t>
-        </is>
-      </c>
-      <c r="Q161" t="inlineStr"/>
-      <c r="R161" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A knowledge or skill that is the duration of experience in related domain held by person source.</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>full-day, 6 years</t>
         </is>
       </c>
       <c r="S161" t="inlineStr"/>
-      <c r="T161" t="inlineStr">
-        <is>
-          <t>course credit</t>
-        </is>
-      </c>
+      <c r="T161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>BCIO:010128</t>
+          <t>BCIO:010106</t>
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr"/>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>supervision of person source</t>
-        </is>
-      </c>
+      <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr"/>
-      <c r="G162" t="inlineStr"/>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>number of people delivering intervention to each participant</t>
+        </is>
+      </c>
       <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr"/>
@@ -6498,38 +6506,34 @@
       <c r="M162" t="inlineStr"/>
       <c r="N162" t="inlineStr">
         <is>
-          <t>A process in which a person source is formally provided, by an individual with appropriate expertise, with corrective and skill-enhancing feedback, regarding the person source’s performance in delivering the intervention.</t>
+          <t>A count data item that is the number of providers that an individual participant in the intervention encounters.</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
       <c r="Q162" t="inlineStr"/>
-      <c r="R162" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
       <c r="S162" t="inlineStr"/>
-      <c r="T162" t="inlineStr">
-        <is>
-          <t>supervised</t>
-        </is>
-      </c>
+      <c r="T162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>BCIO:010129</t>
+          <t>BCIO:010107</t>
         </is>
       </c>
       <c r="B163" t="inlineStr"/>
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr"/>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>volunteering of person source</t>
-        </is>
-      </c>
+      <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr"/>
-      <c r="G163" t="inlineStr"/>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>total number of people able to deliver intervention</t>
+        </is>
+      </c>
       <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr"/>
@@ -6538,21 +6542,17 @@
       <c r="M163" t="inlineStr"/>
       <c r="N163" t="inlineStr">
         <is>
-          <t>A process in which a person source delivers the intervention on a voluntary basis without formal compensation.</t>
+          <t>A count data item that is the total number of providers that are available and able to deliver the intervention.</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
       <c r="Q163" t="inlineStr"/>
-      <c r="R163" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
       <c r="S163" t="inlineStr"/>
-      <c r="T163" t="inlineStr">
-        <is>
-          <t>voluntary basis, volunteering</t>
-        </is>
-      </c>
+      <c r="T163" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
